--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,6 +46,24 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
@@ -55,112 +73,94 @@
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-06-01</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
+    <t>1405-06-02</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>81.52</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G2">
-        <v>85.23999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="H2">
-        <v>89.76000000000001</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>81.52</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G3">
-        <v>81.52</v>
+        <v>79.47</v>
       </c>
       <c r="H3">
-        <v>81.52</v>
+        <v>84.61</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>80.7</v>
+        <v>76.53</v>
       </c>
       <c r="G4">
-        <v>80.7</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H4">
-        <v>80.7</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,13 +718,13 @@
         <v>33</v>
       </c>
       <c r="F5">
-        <v>68.67</v>
+        <v>66.78</v>
       </c>
       <c r="G5">
-        <v>78.05</v>
+        <v>77.58</v>
       </c>
       <c r="H5">
-        <v>88.08</v>
+        <v>88.05</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>74.81</v>
+        <v>53.58</v>
       </c>
       <c r="G6">
-        <v>77.33</v>
+        <v>77.37</v>
       </c>
       <c r="H6">
-        <v>80.91</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -776,13 +776,13 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>73.73</v>
+        <v>74.11</v>
       </c>
       <c r="G7">
-        <v>75.52</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="H7">
-        <v>77.01000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>67.23999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="G8">
-        <v>73.73</v>
+        <v>77.12</v>
       </c>
       <c r="H8">
-        <v>76.23999999999999</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>63.69</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="G9">
-        <v>72.41</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H9">
-        <v>78.45</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>70.17</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G10">
-        <v>72.15000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H10">
-        <v>74.83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>68.38</v>
+        <v>56.57</v>
       </c>
       <c r="G11">
-        <v>71.70999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="H11">
-        <v>76.62</v>
+        <v>77.11</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>65.36</v>
+        <v>65.37</v>
       </c>
       <c r="G12">
-        <v>70.86</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="H12">
-        <v>78.40000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>69.03</v>
+        <v>66.33</v>
       </c>
       <c r="G13">
-        <v>70.39</v>
+        <v>68.72</v>
       </c>
       <c r="H13">
-        <v>73.86</v>
+        <v>70.25</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>69.26000000000001</v>
+        <v>57.42</v>
       </c>
       <c r="G14">
-        <v>70.39</v>
+        <v>68.53</v>
       </c>
       <c r="H14">
-        <v>71.87</v>
+        <v>78.69</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>62.08</v>
+        <v>57.03</v>
       </c>
       <c r="G15">
-        <v>70.15000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="H15">
-        <v>77.11</v>
+        <v>79.31</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>57.16</v>
+        <v>64.98</v>
       </c>
       <c r="G16">
-        <v>69.67</v>
+        <v>67.3</v>
       </c>
       <c r="H16">
-        <v>91.62</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>69.03</v>
+        <v>61.35</v>
       </c>
       <c r="G17">
-        <v>69.43000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="H17">
-        <v>69.66</v>
+        <v>68</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="F18">
-        <v>68</v>
+        <v>53.87</v>
       </c>
       <c r="G18">
-        <v>68.81</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="H18">
-        <v>69.62</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>57.16</v>
+        <v>57.43</v>
       </c>
       <c r="G19">
-        <v>68.73999999999999</v>
+        <v>64.97</v>
       </c>
       <c r="H19">
-        <v>91.62</v>
+        <v>71.63</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F20">
-        <v>54.82</v>
+        <v>58.41</v>
       </c>
       <c r="G20">
-        <v>68.37</v>
+        <v>64.81</v>
       </c>
       <c r="H20">
-        <v>77.16</v>
+        <v>75.31</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>66.72</v>
+        <v>58.95</v>
       </c>
       <c r="G21">
-        <v>68.11</v>
+        <v>64.56</v>
       </c>
       <c r="H21">
-        <v>70.06</v>
+        <v>68.47</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="F22">
-        <v>65.19</v>
+        <v>53.87</v>
       </c>
       <c r="G22">
-        <v>67.34</v>
+        <v>64.41</v>
       </c>
       <c r="H22">
-        <v>69.11</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>60.4</v>
+        <v>63.45</v>
       </c>
       <c r="G23">
-        <v>66.06</v>
+        <v>64.12</v>
       </c>
       <c r="H23">
-        <v>69.47</v>
+        <v>65.66</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>61.82</v>
+        <v>59.17</v>
       </c>
       <c r="G24">
-        <v>65.43000000000001</v>
+        <v>64.11</v>
       </c>
       <c r="H24">
-        <v>70.59</v>
+        <v>71.27</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F25">
-        <v>60.36</v>
+        <v>56.09</v>
       </c>
       <c r="G25">
-        <v>65.28</v>
+        <v>63.92</v>
       </c>
       <c r="H25">
-        <v>70.51000000000001</v>
+        <v>68.08</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F26">
-        <v>61.56</v>
+        <v>60.74</v>
       </c>
       <c r="G26">
-        <v>65.14</v>
+        <v>63.92</v>
       </c>
       <c r="H26">
-        <v>69.06</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27">
-        <v>53.26</v>
+        <v>58.31</v>
       </c>
       <c r="G27">
-        <v>64.61</v>
+        <v>63.77</v>
       </c>
       <c r="H27">
-        <v>79.86</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>54.45</v>
+        <v>61.51</v>
       </c>
       <c r="G28">
-        <v>64.42</v>
+        <v>62.04</v>
       </c>
       <c r="H28">
-        <v>77.54000000000001</v>
+        <v>62.58</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F29">
-        <v>60.82</v>
+        <v>50.8</v>
       </c>
       <c r="G29">
-        <v>64.09</v>
+        <v>61.83</v>
       </c>
       <c r="H29">
-        <v>67.48</v>
+        <v>75.52</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>55.45</v>
+        <v>54.29</v>
       </c>
       <c r="G30">
-        <v>63.4</v>
+        <v>60.67</v>
       </c>
       <c r="H30">
-        <v>77.14</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>57.87</v>
+        <v>55.64</v>
       </c>
       <c r="G31">
-        <v>62.32</v>
+        <v>59.9</v>
       </c>
       <c r="H31">
-        <v>73.55</v>
+        <v>64.58</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>55.91</v>
+        <v>58.69</v>
       </c>
       <c r="G32">
-        <v>61.06</v>
+        <v>59.83</v>
       </c>
       <c r="H32">
-        <v>71.29000000000001</v>
+        <v>61.73</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F33">
-        <v>54.13</v>
+        <v>57.7</v>
       </c>
       <c r="G33">
-        <v>60.14</v>
+        <v>59.64</v>
       </c>
       <c r="H33">
-        <v>71.3</v>
+        <v>63.59</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F34">
-        <v>49.37</v>
+        <v>53.67</v>
       </c>
       <c r="G34">
-        <v>55.64</v>
+        <v>57.25</v>
       </c>
       <c r="H34">
-        <v>63.2</v>
+        <v>61.02</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-02</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
+    <t>1405-06-03</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>74.59999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="G2">
-        <v>80.36</v>
+        <v>81.13</v>
       </c>
       <c r="H2">
-        <v>84.15000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>73.68000000000001</v>
+        <v>78.05</v>
       </c>
       <c r="G3">
-        <v>79.47</v>
+        <v>79.62</v>
       </c>
       <c r="H3">
-        <v>84.61</v>
+        <v>83.03</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>76.53</v>
+        <v>72.92</v>
       </c>
       <c r="G4">
-        <v>78.26000000000001</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="H4">
-        <v>79.34999999999999</v>
+        <v>91.39</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>66.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="G5">
-        <v>77.58</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="H5">
-        <v>88.05</v>
+        <v>80.02</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>53.58</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="G6">
-        <v>77.37</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="H6">
-        <v>89.31999999999999</v>
+        <v>80.02</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -776,13 +776,13 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>74.11</v>
+        <v>75.42</v>
       </c>
       <c r="G7">
-        <v>77.26000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="H7">
-        <v>80.8</v>
+        <v>79.31</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>73.84999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="G8">
-        <v>77.12</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="H8">
-        <v>86.15000000000001</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,13 +834,13 @@
         <v>4</v>
       </c>
       <c r="F9">
-        <v>73.84999999999999</v>
+        <v>72.81</v>
       </c>
       <c r="G9">
-        <v>73.84999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="H9">
-        <v>73.84999999999999</v>
+        <v>76.16</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>72.59999999999999</v>
+        <v>52.38</v>
       </c>
       <c r="G10">
-        <v>72.59999999999999</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H10">
-        <v>72.59999999999999</v>
+        <v>92.52</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>56.57</v>
+        <v>72.92</v>
       </c>
       <c r="G11">
-        <v>70.98999999999999</v>
+        <v>72.92</v>
       </c>
       <c r="H11">
-        <v>77.11</v>
+        <v>72.92</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>65.37</v>
+        <v>68.73</v>
       </c>
       <c r="G12">
-        <v>69.01000000000001</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="H12">
-        <v>72.02</v>
+        <v>74.48</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>66.33</v>
+        <v>64.63</v>
       </c>
       <c r="G13">
-        <v>68.72</v>
+        <v>70.83</v>
       </c>
       <c r="H13">
-        <v>70.25</v>
+        <v>76.83</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>57.42</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="G14">
-        <v>68.53</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="H14">
-        <v>78.69</v>
+        <v>72.64</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>57.03</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="G15">
-        <v>68.45</v>
+        <v>69.69</v>
       </c>
       <c r="H15">
-        <v>79.31</v>
+        <v>71.08</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>64.98</v>
+        <v>62.31</v>
       </c>
       <c r="G16">
-        <v>67.3</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H16">
-        <v>72.84999999999999</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F17">
-        <v>61.35</v>
+        <v>58.48</v>
       </c>
       <c r="G17">
-        <v>65.3</v>
+        <v>69.5</v>
       </c>
       <c r="H17">
-        <v>68</v>
+        <v>85.2</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>53.87</v>
+        <v>61.71</v>
       </c>
       <c r="G18">
-        <v>65.23999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="H18">
-        <v>79.04000000000001</v>
+        <v>78.05</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F19">
-        <v>57.43</v>
+        <v>58.48</v>
       </c>
       <c r="G19">
-        <v>64.97</v>
+        <v>69.13</v>
       </c>
       <c r="H19">
-        <v>71.63</v>
+        <v>85.2</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>58.41</v>
+        <v>63.75</v>
       </c>
       <c r="G20">
-        <v>64.81</v>
+        <v>68.98</v>
       </c>
       <c r="H20">
-        <v>75.31</v>
+        <v>72.5</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F21">
-        <v>58.95</v>
+        <v>57.72</v>
       </c>
       <c r="G21">
-        <v>64.56</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="H21">
-        <v>68.47</v>
+        <v>75.03</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>53.87</v>
+        <v>67.77</v>
       </c>
       <c r="G22">
-        <v>64.41</v>
+        <v>67.77</v>
       </c>
       <c r="H22">
-        <v>79.04000000000001</v>
+        <v>67.77</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F23">
-        <v>63.45</v>
+        <v>56.79</v>
       </c>
       <c r="G23">
-        <v>64.12</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H23">
-        <v>65.66</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>59.17</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G24">
-        <v>64.11</v>
+        <v>66.08</v>
       </c>
       <c r="H24">
-        <v>71.27</v>
+        <v>66.95</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F25">
-        <v>56.09</v>
+        <v>56.71</v>
       </c>
       <c r="G25">
-        <v>63.92</v>
+        <v>65.17</v>
       </c>
       <c r="H25">
-        <v>68.08</v>
+        <v>77.37</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>60.74</v>
+        <v>60.48</v>
       </c>
       <c r="G26">
-        <v>63.92</v>
+        <v>65.02</v>
       </c>
       <c r="H26">
-        <v>66.68000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>58.31</v>
+        <v>57.47</v>
       </c>
       <c r="G27">
-        <v>63.77</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="H27">
-        <v>68.20999999999999</v>
+        <v>71.52</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="F28">
-        <v>61.51</v>
+        <v>55.07</v>
       </c>
       <c r="G28">
-        <v>62.04</v>
+        <v>64.19</v>
       </c>
       <c r="H28">
-        <v>62.58</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>50.8</v>
+        <v>62.84</v>
       </c>
       <c r="G29">
-        <v>61.83</v>
+        <v>64.19</v>
       </c>
       <c r="H29">
-        <v>75.52</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>54.29</v>
+        <v>60.05</v>
       </c>
       <c r="G30">
-        <v>60.67</v>
+        <v>64.12</v>
       </c>
       <c r="H30">
-        <v>69.29000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F31">
-        <v>55.64</v>
+        <v>60.37</v>
       </c>
       <c r="G31">
-        <v>59.9</v>
+        <v>63.86</v>
       </c>
       <c r="H31">
-        <v>64.58</v>
+        <v>68.22</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F32">
-        <v>58.69</v>
+        <v>53.41</v>
       </c>
       <c r="G32">
-        <v>59.83</v>
+        <v>62</v>
       </c>
       <c r="H32">
-        <v>61.73</v>
+        <v>71.44</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F33">
-        <v>57.7</v>
+        <v>56.76</v>
       </c>
       <c r="G33">
-        <v>59.64</v>
+        <v>61.85</v>
       </c>
       <c r="H33">
-        <v>63.59</v>
+        <v>66.67</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F34">
-        <v>53.67</v>
+        <v>58.16</v>
       </c>
       <c r="G34">
-        <v>57.25</v>
+        <v>60.06</v>
       </c>
       <c r="H34">
-        <v>61.02</v>
+        <v>63.87</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,99 +46,99 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
     <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
+    <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
@@ -151,16 +151,16 @@
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-06-03</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
+    <t>1405-06-04</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>64.23999999999999</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="G2">
-        <v>81.13</v>
+        <v>84.19</v>
       </c>
       <c r="H2">
-        <v>90.8</v>
+        <v>92.36</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>78.05</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G3">
-        <v>79.62</v>
+        <v>81.48</v>
       </c>
       <c r="H3">
-        <v>83.03</v>
+        <v>86.08</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>72.92</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="G4">
-        <v>79.51000000000001</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="H4">
-        <v>91.39</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>73.70999999999999</v>
+        <v>59.26</v>
       </c>
       <c r="G5">
-        <v>78.01000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="H5">
-        <v>80.02</v>
+        <v>94.3</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>70.84999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="G6">
-        <v>77.76000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H6">
-        <v>80.02</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>75.42</v>
+        <v>60.94</v>
       </c>
       <c r="G7">
-        <v>77.56</v>
+        <v>78.17</v>
       </c>
       <c r="H7">
-        <v>79.31</v>
+        <v>87.19</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,13 +805,13 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>72.98999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="G8">
-        <v>75.48999999999999</v>
+        <v>78.02</v>
       </c>
       <c r="H8">
-        <v>77.54000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>72.81</v>
+        <v>70.63</v>
       </c>
       <c r="G9">
-        <v>74.98999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="H9">
-        <v>76.16</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>52.38</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="G10">
-        <v>74.06999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="H10">
-        <v>92.52</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>72.92</v>
+        <v>69.5</v>
       </c>
       <c r="G11">
-        <v>72.92</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="H11">
-        <v>72.92</v>
+        <v>83.94</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>68.73</v>
+        <v>69.44</v>
       </c>
       <c r="G12">
-        <v>71.51000000000001</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="H12">
-        <v>74.48</v>
+        <v>82.3</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>64.63</v>
+        <v>68.44</v>
       </c>
       <c r="G13">
-        <v>70.83</v>
+        <v>70.61</v>
       </c>
       <c r="H13">
-        <v>76.83</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>66.84999999999999</v>
+        <v>56.51</v>
       </c>
       <c r="G14">
-        <v>70.06999999999999</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="H14">
-        <v>72.64</v>
+        <v>82.7</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>68.04000000000001</v>
+        <v>60.98</v>
       </c>
       <c r="G15">
-        <v>69.69</v>
+        <v>69.34</v>
       </c>
       <c r="H15">
-        <v>71.08</v>
+        <v>75.61</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>62.31</v>
+        <v>64.12</v>
       </c>
       <c r="G16">
-        <v>69.56999999999999</v>
+        <v>68.89</v>
       </c>
       <c r="H16">
-        <v>76.29000000000001</v>
+        <v>78.97</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>58.48</v>
+        <v>63.74</v>
       </c>
       <c r="G17">
-        <v>69.5</v>
+        <v>68.84</v>
       </c>
       <c r="H17">
-        <v>85.2</v>
+        <v>71.77</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>61.71</v>
+        <v>64.66</v>
       </c>
       <c r="G18">
-        <v>69.22</v>
+        <v>68.66</v>
       </c>
       <c r="H18">
-        <v>78.05</v>
+        <v>72.06</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>58.48</v>
+        <v>60.43</v>
       </c>
       <c r="G19">
-        <v>69.13</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H19">
-        <v>85.2</v>
+        <v>75.16</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>63.75</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G20">
-        <v>68.98</v>
+        <v>68.45</v>
       </c>
       <c r="H20">
-        <v>72.5</v>
+        <v>69.63</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>57.72</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G21">
-        <v>68.70999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="H21">
-        <v>75.03</v>
+        <v>71.45</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>67.77</v>
+        <v>58.57</v>
       </c>
       <c r="G22">
-        <v>67.77</v>
+        <v>67.47</v>
       </c>
       <c r="H22">
-        <v>67.77</v>
+        <v>76.19</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F23">
-        <v>56.79</v>
+        <v>57.04</v>
       </c>
       <c r="G23">
-        <v>66.59999999999999</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="H23">
-        <v>77.93000000000001</v>
+        <v>83.34</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F24">
-        <v>64.90000000000001</v>
+        <v>61.04</v>
       </c>
       <c r="G24">
-        <v>66.08</v>
+        <v>67.2</v>
       </c>
       <c r="H24">
-        <v>66.95</v>
+        <v>71.83</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,13 +1298,13 @@
         <v>37</v>
       </c>
       <c r="F25">
-        <v>56.71</v>
+        <v>61.41</v>
       </c>
       <c r="G25">
-        <v>65.17</v>
+        <v>67.17</v>
       </c>
       <c r="H25">
-        <v>77.37</v>
+        <v>76.39</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>60.48</v>
+        <v>58.69</v>
       </c>
       <c r="G26">
-        <v>65.02</v>
+        <v>66.97</v>
       </c>
       <c r="H26">
-        <v>70.08</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F27">
-        <v>57.47</v>
+        <v>57.04</v>
       </c>
       <c r="G27">
-        <v>64.51000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H27">
-        <v>71.52</v>
+        <v>83.34</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>55.07</v>
+        <v>63.94</v>
       </c>
       <c r="G28">
-        <v>64.19</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="H28">
-        <v>75.04000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>62.84</v>
+        <v>56.65</v>
       </c>
       <c r="G29">
-        <v>64.19</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="H29">
-        <v>65.54000000000001</v>
+        <v>70.61</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>60.05</v>
+        <v>61.89</v>
       </c>
       <c r="G30">
-        <v>64.12</v>
+        <v>63.57</v>
       </c>
       <c r="H30">
-        <v>66.92</v>
+        <v>65.08</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F31">
-        <v>60.37</v>
+        <v>55.15</v>
       </c>
       <c r="G31">
-        <v>63.86</v>
+        <v>63.54</v>
       </c>
       <c r="H31">
-        <v>68.22</v>
+        <v>70.98</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="F32">
-        <v>53.41</v>
+        <v>51.86</v>
       </c>
       <c r="G32">
-        <v>62</v>
+        <v>62.38</v>
       </c>
       <c r="H32">
-        <v>71.44</v>
+        <v>75.73</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,13 +1530,13 @@
         <v>16</v>
       </c>
       <c r="F33">
-        <v>56.76</v>
+        <v>58.26</v>
       </c>
       <c r="G33">
-        <v>61.85</v>
+        <v>62.26</v>
       </c>
       <c r="H33">
-        <v>66.67</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,13 +1559,13 @@
         <v>12</v>
       </c>
       <c r="F34">
-        <v>58.16</v>
+        <v>58.31</v>
       </c>
       <c r="G34">
-        <v>60.06</v>
+        <v>61.27</v>
       </c>
       <c r="H34">
-        <v>63.87</v>
+        <v>67.97</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
+    <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-06-04</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
+    <t>1405-06-05</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>79.79000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="G2">
-        <v>84.19</v>
+        <v>80.98</v>
       </c>
       <c r="H2">
-        <v>92.36</v>
+        <v>82.17</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>76.59999999999999</v>
+        <v>73.56</v>
       </c>
       <c r="G3">
-        <v>81.48</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="H3">
-        <v>86.08</v>
+        <v>89.25</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>79.79000000000001</v>
+        <v>74.12</v>
       </c>
       <c r="G4">
-        <v>79.79000000000001</v>
+        <v>79.88</v>
       </c>
       <c r="H4">
-        <v>79.79000000000001</v>
+        <v>83.75</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>59.26</v>
+        <v>73.38</v>
       </c>
       <c r="G5">
-        <v>79.12</v>
+        <v>79.64</v>
       </c>
       <c r="H5">
-        <v>94.3</v>
+        <v>86.87</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>78.26000000000001</v>
+        <v>63.85</v>
       </c>
       <c r="G6">
-        <v>78.26000000000001</v>
+        <v>78.22</v>
       </c>
       <c r="H6">
-        <v>78.26000000000001</v>
+        <v>84.81</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>60.94</v>
+        <v>69.94</v>
       </c>
       <c r="G7">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="H7">
-        <v>87.19</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>75.42</v>
+        <v>63.44</v>
       </c>
       <c r="G8">
-        <v>78.02</v>
+        <v>78.03</v>
       </c>
       <c r="H8">
-        <v>82.12</v>
+        <v>85.16</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>70.63</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="G9">
-        <v>77.7</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="H9">
-        <v>85.01000000000001</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,13 +863,13 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>72.26000000000001</v>
+        <v>69.94</v>
       </c>
       <c r="G10">
-        <v>76.3</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="H10">
-        <v>79.43000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>69.5</v>
+        <v>62.8</v>
       </c>
       <c r="G11">
-        <v>73.20999999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="H11">
-        <v>83.94</v>
+        <v>81.59</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>69.44</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="G12">
-        <v>73.06999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="H12">
-        <v>82.3</v>
+        <v>73.63</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>68.44</v>
+        <v>70.37</v>
       </c>
       <c r="G13">
-        <v>70.61</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="H13">
-        <v>72.04000000000001</v>
+        <v>73.66</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>56.51</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="G14">
-        <v>69.79000000000001</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="H14">
-        <v>82.7</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>60.98</v>
+        <v>64.09</v>
       </c>
       <c r="G15">
-        <v>69.34</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="H15">
-        <v>75.61</v>
+        <v>77.45</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>64.12</v>
+        <v>63.03</v>
       </c>
       <c r="G16">
-        <v>68.89</v>
+        <v>68.86</v>
       </c>
       <c r="H16">
-        <v>78.97</v>
+        <v>72.5</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>63.74</v>
+        <v>65.08</v>
       </c>
       <c r="G17">
-        <v>68.84</v>
+        <v>68.2</v>
       </c>
       <c r="H17">
-        <v>71.77</v>
+        <v>73.89</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>64.66</v>
+        <v>58.11</v>
       </c>
       <c r="G18">
-        <v>68.66</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="H18">
-        <v>72.06</v>
+        <v>71.02</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>60.43</v>
+        <v>65.95</v>
       </c>
       <c r="G19">
-        <v>68.65000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="H19">
-        <v>75.16</v>
+        <v>68.02</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>67.09999999999999</v>
+        <v>63.34</v>
       </c>
       <c r="G20">
-        <v>68.45</v>
+        <v>66.84</v>
       </c>
       <c r="H20">
-        <v>69.63</v>
+        <v>69.36</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>64.09999999999999</v>
+        <v>63.44</v>
       </c>
       <c r="G21">
-        <v>67.95999999999999</v>
+        <v>66.63</v>
       </c>
       <c r="H21">
-        <v>71.45</v>
+        <v>69.7</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F22">
-        <v>58.57</v>
+        <v>53.48</v>
       </c>
       <c r="G22">
-        <v>67.47</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="H22">
-        <v>76.19</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,13 +1240,13 @@
         <v>65</v>
       </c>
       <c r="F23">
-        <v>57.04</v>
+        <v>55.6</v>
       </c>
       <c r="G23">
-        <v>67.29000000000001</v>
+        <v>66.11</v>
       </c>
       <c r="H23">
-        <v>83.34</v>
+        <v>83.48</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>61.04</v>
+        <v>61.27</v>
       </c>
       <c r="G24">
-        <v>67.2</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="H24">
-        <v>71.83</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>61.41</v>
+        <v>58.68</v>
       </c>
       <c r="G25">
-        <v>67.17</v>
+        <v>65.27</v>
       </c>
       <c r="H25">
-        <v>76.39</v>
+        <v>69.37</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F26">
-        <v>58.69</v>
+        <v>55.46</v>
       </c>
       <c r="G26">
-        <v>66.97</v>
+        <v>64.78</v>
       </c>
       <c r="H26">
-        <v>77.06999999999999</v>
+        <v>83.48</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>57.04</v>
+        <v>55.49</v>
       </c>
       <c r="G27">
-        <v>66.84999999999999</v>
+        <v>63.56</v>
       </c>
       <c r="H27">
-        <v>83.34</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>63.94</v>
+        <v>61.08</v>
       </c>
       <c r="G28">
-        <v>66.20999999999999</v>
+        <v>63.49</v>
       </c>
       <c r="H28">
-        <v>68.48</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F29">
-        <v>56.65</v>
+        <v>52.16</v>
       </c>
       <c r="G29">
-        <v>64.65000000000001</v>
+        <v>61.39</v>
       </c>
       <c r="H29">
-        <v>70.61</v>
+        <v>71.19</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F30">
-        <v>61.89</v>
+        <v>56.13</v>
       </c>
       <c r="G30">
-        <v>63.57</v>
+        <v>60.51</v>
       </c>
       <c r="H30">
-        <v>65.08</v>
+        <v>64.88</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>55.15</v>
+        <v>52.22</v>
       </c>
       <c r="G31">
-        <v>63.54</v>
+        <v>60.26</v>
       </c>
       <c r="H31">
-        <v>70.98</v>
+        <v>77.47</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F32">
-        <v>51.86</v>
+        <v>57</v>
       </c>
       <c r="G32">
-        <v>62.38</v>
+        <v>60.21</v>
       </c>
       <c r="H32">
-        <v>75.73</v>
+        <v>68.42</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F33">
-        <v>58.26</v>
+        <v>54.26</v>
       </c>
       <c r="G33">
-        <v>62.26</v>
+        <v>59.86</v>
       </c>
       <c r="H33">
-        <v>67.18000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>58.31</v>
+        <v>55.02</v>
       </c>
       <c r="G34">
-        <v>61.27</v>
+        <v>59.15</v>
       </c>
       <c r="H34">
-        <v>67.97</v>
+        <v>70.06</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-05</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
+    <t>1405-06-06</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>80.09</v>
+        <v>72.84</v>
       </c>
       <c r="G2">
-        <v>80.98</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="H2">
-        <v>82.17</v>
+        <v>86.02</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>73.56</v>
+        <v>71.83</v>
       </c>
       <c r="G3">
-        <v>80.68000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="H3">
-        <v>89.25</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>74.12</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G4">
-        <v>79.88</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="H4">
-        <v>83.75</v>
+        <v>84.56</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>73.38</v>
+        <v>74.05</v>
       </c>
       <c r="G5">
-        <v>79.64</v>
+        <v>78.05</v>
       </c>
       <c r="H5">
-        <v>86.87</v>
+        <v>82.72</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>63.85</v>
+        <v>69.92</v>
       </c>
       <c r="G6">
-        <v>78.22</v>
+        <v>76.5</v>
       </c>
       <c r="H6">
-        <v>84.81</v>
+        <v>80.02</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>69.94</v>
+        <v>73.81</v>
       </c>
       <c r="G7">
-        <v>78.06999999999999</v>
+        <v>73.81</v>
       </c>
       <c r="H7">
-        <v>83.84999999999999</v>
+        <v>73.81</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>63.44</v>
+        <v>62.39</v>
       </c>
       <c r="G8">
-        <v>78.03</v>
+        <v>73.23</v>
       </c>
       <c r="H8">
-        <v>85.16</v>
+        <v>84.58</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>77.68000000000001</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="G9">
-        <v>77.68000000000001</v>
+        <v>72.58</v>
       </c>
       <c r="H9">
-        <v>77.68000000000001</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>69.94</v>
+        <v>62.13</v>
       </c>
       <c r="G10">
-        <v>75.15000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H10">
-        <v>79.55</v>
+        <v>82.3</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>62.8</v>
+        <v>61.51</v>
       </c>
       <c r="G11">
-        <v>74.84999999999999</v>
+        <v>71.66</v>
       </c>
       <c r="H11">
-        <v>81.59</v>
+        <v>77.63</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>69.84999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="G12">
-        <v>72.5</v>
+        <v>71.08</v>
       </c>
       <c r="H12">
-        <v>73.63</v>
+        <v>79.56</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>70.37</v>
+        <v>57.91</v>
       </c>
       <c r="G13">
-        <v>71.51000000000001</v>
+        <v>70.52</v>
       </c>
       <c r="H13">
-        <v>73.66</v>
+        <v>78.5</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F14">
-        <v>70.43000000000001</v>
+        <v>61.46</v>
       </c>
       <c r="G14">
-        <v>70.43000000000001</v>
+        <v>70.17</v>
       </c>
       <c r="H14">
-        <v>70.43000000000001</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15">
-        <v>64.09</v>
+        <v>61.55</v>
       </c>
       <c r="G15">
-        <v>69.93000000000001</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="H15">
-        <v>77.45</v>
+        <v>74.39</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F16">
-        <v>63.03</v>
+        <v>58.76</v>
       </c>
       <c r="G16">
-        <v>68.86</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H16">
-        <v>72.5</v>
+        <v>82.12</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>65.08</v>
+        <v>58.37</v>
       </c>
       <c r="G17">
-        <v>68.2</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H17">
-        <v>73.89</v>
+        <v>75.03</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>58.11</v>
+        <v>64.95</v>
       </c>
       <c r="G18">
-        <v>67.04000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="H18">
-        <v>71.02</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>65.95</v>
+        <v>63.43</v>
       </c>
       <c r="G19">
-        <v>66.98</v>
+        <v>67.63</v>
       </c>
       <c r="H19">
-        <v>68.02</v>
+        <v>72.56</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>63.34</v>
+        <v>56.15</v>
       </c>
       <c r="G20">
-        <v>66.84</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="H20">
-        <v>69.36</v>
+        <v>90.42</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="F21">
-        <v>63.44</v>
+        <v>55.64</v>
       </c>
       <c r="G21">
-        <v>66.63</v>
+        <v>65.23</v>
       </c>
       <c r="H21">
-        <v>69.7</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>53.48</v>
+        <v>59.89</v>
       </c>
       <c r="G22">
-        <v>66.20999999999999</v>
+        <v>65.22</v>
       </c>
       <c r="H22">
-        <v>71.18000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="F23">
-        <v>55.6</v>
+        <v>56.15</v>
       </c>
       <c r="G23">
-        <v>66.11</v>
+        <v>64.94</v>
       </c>
       <c r="H23">
-        <v>83.48</v>
+        <v>73.38</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="F24">
-        <v>61.27</v>
+        <v>55.62</v>
       </c>
       <c r="G24">
-        <v>65.45999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="H24">
-        <v>69.31999999999999</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>58.68</v>
+        <v>55.32</v>
       </c>
       <c r="G25">
-        <v>65.27</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="H25">
-        <v>69.37</v>
+        <v>72.8</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>55.46</v>
+        <v>64.33</v>
       </c>
       <c r="G26">
-        <v>64.78</v>
+        <v>64.33</v>
       </c>
       <c r="H26">
-        <v>83.48</v>
+        <v>64.33</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>55.49</v>
+        <v>57.91</v>
       </c>
       <c r="G27">
-        <v>63.56</v>
+        <v>64</v>
       </c>
       <c r="H27">
-        <v>76.43000000000001</v>
+        <v>70.42</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F28">
-        <v>61.08</v>
+        <v>54.91</v>
       </c>
       <c r="G28">
-        <v>63.49</v>
+        <v>63.75</v>
       </c>
       <c r="H28">
-        <v>66.29000000000001</v>
+        <v>74.37</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>52.16</v>
+        <v>62.67</v>
       </c>
       <c r="G29">
-        <v>61.39</v>
+        <v>62.98</v>
       </c>
       <c r="H29">
-        <v>71.19</v>
+        <v>63.3</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>56.13</v>
+        <v>59.73</v>
       </c>
       <c r="G30">
-        <v>60.51</v>
+        <v>62.86</v>
       </c>
       <c r="H30">
-        <v>64.88</v>
+        <v>65.7</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>52.22</v>
+        <v>55.19</v>
       </c>
       <c r="G31">
-        <v>60.26</v>
+        <v>61.85</v>
       </c>
       <c r="H31">
-        <v>77.47</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>57</v>
+        <v>55.83</v>
       </c>
       <c r="G32">
-        <v>60.21</v>
+        <v>61.29</v>
       </c>
       <c r="H32">
-        <v>68.42</v>
+        <v>66.17</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F33">
-        <v>54.26</v>
+        <v>56.58</v>
       </c>
       <c r="G33">
-        <v>59.86</v>
+        <v>61.06</v>
       </c>
       <c r="H33">
-        <v>66.5</v>
+        <v>66.37</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>55.02</v>
+        <v>56.94</v>
       </c>
       <c r="G34">
-        <v>59.15</v>
+        <v>60.44</v>
       </c>
       <c r="H34">
-        <v>70.06</v>
+        <v>65.97</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-06-06</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
+    <t>1405-06-07</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>72.84</v>
+        <v>84.38</v>
       </c>
       <c r="G2">
-        <v>79.65000000000001</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="H2">
-        <v>86.02</v>
+        <v>89.86</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>71.83</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G3">
-        <v>79.12</v>
+        <v>86.78</v>
       </c>
       <c r="H3">
-        <v>86.23999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>69.59999999999999</v>
+        <v>60.23</v>
       </c>
       <c r="G4">
-        <v>78.76000000000001</v>
+        <v>85.62</v>
       </c>
       <c r="H4">
-        <v>84.56</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>74.05</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="G5">
-        <v>78.05</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="H5">
-        <v>82.72</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>69.92</v>
+        <v>73.66</v>
       </c>
       <c r="G6">
-        <v>76.5</v>
+        <v>80.66</v>
       </c>
       <c r="H6">
-        <v>80.02</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>73.81</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G7">
-        <v>73.81</v>
+        <v>78.44</v>
       </c>
       <c r="H7">
-        <v>73.81</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>62.39</v>
+        <v>65.83</v>
       </c>
       <c r="G8">
-        <v>73.23</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="H8">
-        <v>84.58</v>
+        <v>82.69</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>71.31999999999999</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="G9">
-        <v>72.58</v>
+        <v>74.36</v>
       </c>
       <c r="H9">
-        <v>75.29000000000001</v>
+        <v>78.81</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>62.13</v>
+        <v>64.59</v>
       </c>
       <c r="G10">
-        <v>71.79000000000001</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H10">
-        <v>82.3</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>61.51</v>
+        <v>71.86</v>
       </c>
       <c r="G11">
-        <v>71.66</v>
+        <v>72.88</v>
       </c>
       <c r="H11">
-        <v>77.63</v>
+        <v>74.92</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>61.2</v>
+        <v>70.83</v>
       </c>
       <c r="G12">
-        <v>71.08</v>
+        <v>71.98</v>
       </c>
       <c r="H12">
-        <v>79.56</v>
+        <v>73.09</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>57.91</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="G13">
-        <v>70.52</v>
+        <v>70.37</v>
       </c>
       <c r="H13">
-        <v>78.5</v>
+        <v>77.81</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>61.46</v>
+        <v>57.78</v>
       </c>
       <c r="G14">
-        <v>70.17</v>
+        <v>70.2</v>
       </c>
       <c r="H14">
-        <v>91.70999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>61.55</v>
+        <v>59.74</v>
       </c>
       <c r="G15">
-        <v>69.48999999999999</v>
+        <v>69.48</v>
       </c>
       <c r="H15">
-        <v>74.39</v>
+        <v>75.17</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>58.76</v>
+        <v>58.37</v>
       </c>
       <c r="G16">
-        <v>69.20999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="H16">
-        <v>82.12</v>
+        <v>87.87</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>58.37</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="G17">
-        <v>68.48999999999999</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H17">
-        <v>75.03</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F18">
-        <v>64.95</v>
+        <v>54.32</v>
       </c>
       <c r="G18">
-        <v>68.25</v>
+        <v>66.58</v>
       </c>
       <c r="H18">
-        <v>72.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>63.43</v>
+        <v>58.62</v>
       </c>
       <c r="G19">
-        <v>67.63</v>
+        <v>65.84</v>
       </c>
       <c r="H19">
-        <v>72.56</v>
+        <v>78.17</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>56.15</v>
+        <v>54.02</v>
       </c>
       <c r="G20">
-        <v>65.51000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="H20">
-        <v>90.42</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>55.64</v>
+        <v>60.68</v>
       </c>
       <c r="G21">
-        <v>65.23</v>
+        <v>65.08</v>
       </c>
       <c r="H21">
-        <v>85.95999999999999</v>
+        <v>68.13</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>59.89</v>
+        <v>58.9</v>
       </c>
       <c r="G22">
-        <v>65.22</v>
+        <v>65.02</v>
       </c>
       <c r="H22">
-        <v>74.90000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>56.15</v>
+        <v>55.35</v>
       </c>
       <c r="G23">
-        <v>64.94</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="H23">
-        <v>73.38</v>
+        <v>70.83</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,13 +1269,13 @@
         <v>117</v>
       </c>
       <c r="F24">
-        <v>55.62</v>
+        <v>54.19</v>
       </c>
       <c r="G24">
-        <v>64.81999999999999</v>
+        <v>64.36</v>
       </c>
       <c r="H24">
-        <v>85.95999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F25">
-        <v>55.32</v>
+        <v>54.7</v>
       </c>
       <c r="G25">
-        <v>64.81999999999999</v>
+        <v>64.19</v>
       </c>
       <c r="H25">
-        <v>72.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>64.33</v>
+        <v>59.85</v>
       </c>
       <c r="G26">
-        <v>64.33</v>
+        <v>63.46</v>
       </c>
       <c r="H26">
-        <v>64.33</v>
+        <v>68.87</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>57.91</v>
+        <v>58.82</v>
       </c>
       <c r="G27">
-        <v>64</v>
+        <v>63.25</v>
       </c>
       <c r="H27">
-        <v>70.42</v>
+        <v>68</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>54.91</v>
+        <v>61.55</v>
       </c>
       <c r="G28">
-        <v>63.75</v>
+        <v>62.42</v>
       </c>
       <c r="H28">
-        <v>74.37</v>
+        <v>63.34</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F29">
-        <v>62.67</v>
+        <v>52.29</v>
       </c>
       <c r="G29">
-        <v>62.98</v>
+        <v>61.59</v>
       </c>
       <c r="H29">
-        <v>63.3</v>
+        <v>69.13</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>59.73</v>
+        <v>56.13</v>
       </c>
       <c r="G30">
-        <v>62.86</v>
+        <v>61.3</v>
       </c>
       <c r="H30">
-        <v>65.7</v>
+        <v>63.77</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,13 +1472,13 @@
         <v>37</v>
       </c>
       <c r="F31">
-        <v>55.19</v>
+        <v>53.27</v>
       </c>
       <c r="G31">
-        <v>61.85</v>
+        <v>60.76</v>
       </c>
       <c r="H31">
-        <v>70.01000000000001</v>
+        <v>66.97</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>55.83</v>
+        <v>54.8</v>
       </c>
       <c r="G32">
-        <v>61.29</v>
+        <v>60.63</v>
       </c>
       <c r="H32">
-        <v>66.17</v>
+        <v>64.75</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,13 +1530,13 @@
         <v>12</v>
       </c>
       <c r="F33">
-        <v>56.58</v>
+        <v>55.28</v>
       </c>
       <c r="G33">
-        <v>61.06</v>
+        <v>59.14</v>
       </c>
       <c r="H33">
-        <v>66.37</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>56.94</v>
+        <v>56.56</v>
       </c>
       <c r="G34">
-        <v>60.44</v>
+        <v>57.48</v>
       </c>
       <c r="H34">
-        <v>65.97</v>
+        <v>58.39</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-06-07</t>
-  </si>
-  <si>
-    <t>2026-08-29</t>
+    <t>1405-06-08</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>84.38</v>
+        <v>85.12</v>
       </c>
       <c r="G2">
-        <v>87.65000000000001</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="H2">
-        <v>89.86</v>
+        <v>101.35</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>73.09999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="G3">
-        <v>86.78</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="H3">
-        <v>92.81</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,13 +689,13 @@
         <v>28</v>
       </c>
       <c r="F4">
-        <v>60.23</v>
+        <v>69.8</v>
       </c>
       <c r="G4">
-        <v>85.62</v>
+        <v>82.39</v>
       </c>
       <c r="H4">
-        <v>92.98999999999999</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>81.51000000000001</v>
+        <v>57.87</v>
       </c>
       <c r="G5">
-        <v>81.51000000000001</v>
+        <v>81.91</v>
       </c>
       <c r="H5">
-        <v>81.51000000000001</v>
+        <v>99.27</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>73.66</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="G6">
-        <v>80.66</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H6">
-        <v>86.45999999999999</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>78.09999999999999</v>
+        <v>63.23</v>
       </c>
       <c r="G7">
-        <v>78.44</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="H7">
-        <v>78.76000000000001</v>
+        <v>88.75</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>65.83</v>
+        <v>77.84</v>
       </c>
       <c r="G8">
-        <v>74.45999999999999</v>
+        <v>79.41</v>
       </c>
       <c r="H8">
-        <v>82.69</v>
+        <v>82.72</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>70.73999999999999</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="G9">
-        <v>74.36</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="H9">
-        <v>78.81</v>
+        <v>80.62</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>64.59</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="G10">
-        <v>74.06999999999999</v>
+        <v>76.88</v>
       </c>
       <c r="H10">
-        <v>82.73999999999999</v>
+        <v>78.39</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>71.86</v>
+        <v>66.88</v>
       </c>
       <c r="G11">
-        <v>72.88</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H11">
-        <v>74.92</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>70.83</v>
+        <v>70.19</v>
       </c>
       <c r="G12">
-        <v>71.98</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H12">
-        <v>73.09</v>
+        <v>88.36</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>65.81999999999999</v>
+        <v>61.88</v>
       </c>
       <c r="G13">
-        <v>70.37</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="H13">
-        <v>77.81</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>57.78</v>
+        <v>66.91</v>
       </c>
       <c r="G14">
-        <v>70.2</v>
+        <v>73.53</v>
       </c>
       <c r="H14">
-        <v>78.84</v>
+        <v>80.98</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1008,16 +1008,16 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>59.74</v>
+        <v>64.37</v>
       </c>
       <c r="G15">
-        <v>69.48</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="H15">
-        <v>75.17</v>
+        <v>76.62</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F16">
-        <v>58.37</v>
+        <v>57.96</v>
       </c>
       <c r="G16">
-        <v>69.15000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H16">
-        <v>87.87</v>
+        <v>85.13</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>68.01000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="G17">
-        <v>68.01000000000001</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H17">
-        <v>68.01000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="F18">
-        <v>54.32</v>
+        <v>57.96</v>
       </c>
       <c r="G18">
-        <v>66.58</v>
+        <v>68.14</v>
       </c>
       <c r="H18">
-        <v>80.59999999999999</v>
+        <v>85.13</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>58.62</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G19">
-        <v>65.84</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H19">
-        <v>78.17</v>
+        <v>68.09</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F20">
-        <v>54.02</v>
+        <v>55.04</v>
       </c>
       <c r="G20">
-        <v>65.15000000000001</v>
+        <v>67.47</v>
       </c>
       <c r="H20">
-        <v>71.20999999999999</v>
+        <v>78.53</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>60.68</v>
+        <v>59.98</v>
       </c>
       <c r="G21">
-        <v>65.08</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="H21">
-        <v>68.13</v>
+        <v>76.77</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F22">
-        <v>58.9</v>
+        <v>55.57</v>
       </c>
       <c r="G22">
-        <v>65.02</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="H22">
-        <v>78.34999999999999</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>55.35</v>
+        <v>57.04</v>
       </c>
       <c r="G23">
-        <v>64.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H23">
-        <v>70.83</v>
+        <v>71.94</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>54.19</v>
+        <v>64.16</v>
       </c>
       <c r="G24">
-        <v>64.36</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="H24">
-        <v>84.59999999999999</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>54.7</v>
+        <v>61.48</v>
       </c>
       <c r="G25">
-        <v>64.19</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="H25">
-        <v>84.59999999999999</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>59.85</v>
+        <v>56.03</v>
       </c>
       <c r="G26">
-        <v>63.46</v>
+        <v>64.7</v>
       </c>
       <c r="H26">
-        <v>68.87</v>
+        <v>73.25</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F27">
-        <v>58.82</v>
+        <v>61.95</v>
       </c>
       <c r="G27">
-        <v>63.25</v>
+        <v>64.11</v>
       </c>
       <c r="H27">
-        <v>68</v>
+        <v>66.47</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F28">
-        <v>61.55</v>
+        <v>57.72</v>
       </c>
       <c r="G28">
-        <v>62.42</v>
+        <v>63.02</v>
       </c>
       <c r="H28">
-        <v>63.34</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>52.29</v>
+        <v>59.16</v>
       </c>
       <c r="G29">
-        <v>61.59</v>
+        <v>62.53</v>
       </c>
       <c r="H29">
-        <v>69.13</v>
+        <v>67.13</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>56.13</v>
+        <v>58.33</v>
       </c>
       <c r="G30">
-        <v>61.3</v>
+        <v>62.53</v>
       </c>
       <c r="H30">
-        <v>63.77</v>
+        <v>69.2</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>53.27</v>
+        <v>55.34</v>
       </c>
       <c r="G31">
-        <v>60.76</v>
+        <v>61.36</v>
       </c>
       <c r="H31">
-        <v>66.97</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>54.8</v>
+        <v>57.79</v>
       </c>
       <c r="G32">
-        <v>60.63</v>
+        <v>61.24</v>
       </c>
       <c r="H32">
-        <v>64.75</v>
+        <v>65.7</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>55.28</v>
+        <v>56.85</v>
       </c>
       <c r="G33">
-        <v>59.14</v>
+        <v>61.07</v>
       </c>
       <c r="H33">
-        <v>64.29000000000001</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F34">
-        <v>56.56</v>
+        <v>54.68</v>
       </c>
       <c r="G34">
-        <v>57.48</v>
+        <v>60.69</v>
       </c>
       <c r="H34">
-        <v>58.39</v>
+        <v>76.08</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-06-08</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
+    <t>1405-06-09</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>85.12</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="G2">
-        <v>91.34999999999999</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="H2">
-        <v>101.35</v>
+        <v>96.23</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>85.56999999999999</v>
+        <v>76.98</v>
       </c>
       <c r="G3">
-        <v>85.56999999999999</v>
+        <v>81.92</v>
       </c>
       <c r="H3">
-        <v>85.56999999999999</v>
+        <v>87.09</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>69.8</v>
+        <v>79.19</v>
       </c>
       <c r="G4">
-        <v>82.39</v>
+        <v>79.19</v>
       </c>
       <c r="H4">
-        <v>89.70999999999999</v>
+        <v>79.19</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>57.87</v>
+        <v>73.7</v>
       </c>
       <c r="G5">
-        <v>81.91</v>
+        <v>77.44</v>
       </c>
       <c r="H5">
-        <v>99.27</v>
+        <v>79.47</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>80.93000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="G6">
-        <v>80.93000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="H6">
-        <v>80.93000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,13 +776,13 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>63.23</v>
+        <v>62.3</v>
       </c>
       <c r="G7">
-        <v>80.04000000000001</v>
+        <v>76.12</v>
       </c>
       <c r="H7">
-        <v>88.75</v>
+        <v>80.92</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>77.84</v>
+        <v>73.66</v>
       </c>
       <c r="G8">
-        <v>79.41</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="H8">
-        <v>82.72</v>
+        <v>78.75</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>74.18000000000001</v>
+        <v>57.07</v>
       </c>
       <c r="G9">
-        <v>77.70999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="H9">
-        <v>80.62</v>
+        <v>82.75</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>76.06999999999999</v>
+        <v>61.77</v>
       </c>
       <c r="G10">
-        <v>76.88</v>
+        <v>75.27</v>
       </c>
       <c r="H10">
-        <v>78.39</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>66.88</v>
+        <v>74.19</v>
       </c>
       <c r="G11">
-        <v>76.84999999999999</v>
+        <v>75.22</v>
       </c>
       <c r="H11">
-        <v>79.09999999999999</v>
+        <v>76.37</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>70.19</v>
+        <v>74.36</v>
       </c>
       <c r="G12">
-        <v>76.84999999999999</v>
+        <v>75.12</v>
       </c>
       <c r="H12">
-        <v>88.36</v>
+        <v>77.12</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>61.88</v>
+        <v>63.79</v>
       </c>
       <c r="G13">
-        <v>74.73999999999999</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="H13">
-        <v>84.43000000000001</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>66.91</v>
+        <v>62.86</v>
       </c>
       <c r="G14">
-        <v>73.53</v>
+        <v>69.36</v>
       </c>
       <c r="H14">
-        <v>80.98</v>
+        <v>73.56</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,16 +1008,16 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>64.37</v>
+        <v>59.05</v>
       </c>
       <c r="G15">
-        <v>71.98999999999999</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="H15">
-        <v>76.62</v>
+        <v>75.16</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,13 +1037,13 @@
         <v>65</v>
       </c>
       <c r="F16">
-        <v>57.96</v>
+        <v>58.59</v>
       </c>
       <c r="G16">
-        <v>68.56999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="H16">
-        <v>85.13</v>
+        <v>83.05</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="F17">
-        <v>65.51000000000001</v>
+        <v>58.59</v>
       </c>
       <c r="G17">
-        <v>68.48999999999999</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="H17">
-        <v>72.23</v>
+        <v>83.05</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>57.96</v>
+        <v>63.3</v>
       </c>
       <c r="G18">
-        <v>68.14</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="H18">
-        <v>85.13</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>67.59999999999999</v>
+        <v>60.72</v>
       </c>
       <c r="G19">
-        <v>67.84999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="H19">
-        <v>68.09</v>
+        <v>72.92</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,13 +1153,13 @@
         <v>62</v>
       </c>
       <c r="F20">
-        <v>55.04</v>
+        <v>55.18</v>
       </c>
       <c r="G20">
-        <v>67.47</v>
+        <v>67.03</v>
       </c>
       <c r="H20">
-        <v>78.53</v>
+        <v>74.28</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>59.98</v>
+        <v>58.19</v>
       </c>
       <c r="G21">
-        <v>67.29000000000001</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="H21">
-        <v>76.77</v>
+        <v>80.92</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>55.57</v>
+        <v>59.26</v>
       </c>
       <c r="G22">
-        <v>66.81999999999999</v>
+        <v>66.06</v>
       </c>
       <c r="H22">
-        <v>79.18000000000001</v>
+        <v>70.61</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>57.04</v>
+        <v>63.66</v>
       </c>
       <c r="G23">
-        <v>65.90000000000001</v>
+        <v>65.05</v>
       </c>
       <c r="H23">
-        <v>71.94</v>
+        <v>66.44</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>64.16</v>
+        <v>59.8</v>
       </c>
       <c r="G24">
-        <v>65.65000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="H24">
-        <v>68.18000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>61.48</v>
+        <v>58.2</v>
       </c>
       <c r="G25">
-        <v>65.15000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="H25">
-        <v>69.45999999999999</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>56.03</v>
+        <v>58.91</v>
       </c>
       <c r="G26">
-        <v>64.7</v>
+        <v>63.61</v>
       </c>
       <c r="H26">
-        <v>73.25</v>
+        <v>67.87</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F27">
-        <v>61.95</v>
+        <v>55.71</v>
       </c>
       <c r="G27">
-        <v>64.11</v>
+        <v>62.69</v>
       </c>
       <c r="H27">
-        <v>66.47</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>57.72</v>
+        <v>57.37</v>
       </c>
       <c r="G28">
-        <v>63.02</v>
+        <v>62.63</v>
       </c>
       <c r="H28">
-        <v>71.68000000000001</v>
+        <v>69.02</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>59.16</v>
+        <v>57.83</v>
       </c>
       <c r="G29">
-        <v>62.53</v>
+        <v>62.14</v>
       </c>
       <c r="H29">
-        <v>67.13</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F30">
-        <v>58.33</v>
+        <v>58.2</v>
       </c>
       <c r="G30">
-        <v>62.53</v>
+        <v>61.9</v>
       </c>
       <c r="H30">
-        <v>69.2</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>55.34</v>
+        <v>55.08</v>
       </c>
       <c r="G31">
-        <v>61.36</v>
+        <v>60.91</v>
       </c>
       <c r="H31">
-        <v>65.51000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,13 +1501,13 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>57.79</v>
+        <v>55.03</v>
       </c>
       <c r="G32">
-        <v>61.24</v>
+        <v>60.69</v>
       </c>
       <c r="H32">
-        <v>65.7</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F33">
-        <v>56.85</v>
+        <v>56.66</v>
       </c>
       <c r="G33">
-        <v>61.07</v>
+        <v>60.54</v>
       </c>
       <c r="H33">
-        <v>65.18000000000001</v>
+        <v>66.14</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>54.68</v>
+        <v>56.2</v>
       </c>
       <c r="G34">
-        <v>60.69</v>
+        <v>58.4</v>
       </c>
       <c r="H34">
-        <v>76.08</v>
+        <v>59.97</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
   </si>
   <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-09</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
+    <t>1405-06-10</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>80.18000000000001</v>
+        <v>136.98</v>
       </c>
       <c r="G2">
-        <v>86.29000000000001</v>
+        <v>138.64</v>
       </c>
       <c r="H2">
-        <v>96.23</v>
+        <v>140.65</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>76.98</v>
+        <v>94.41</v>
       </c>
       <c r="G3">
-        <v>81.92</v>
+        <v>105.87</v>
       </c>
       <c r="H3">
-        <v>87.09</v>
+        <v>120.54</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>79.19</v>
+        <v>80.3</v>
       </c>
       <c r="G4">
-        <v>79.19</v>
+        <v>92.8</v>
       </c>
       <c r="H4">
-        <v>79.19</v>
+        <v>109.4</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>73.7</v>
+        <v>74.16</v>
       </c>
       <c r="G5">
-        <v>77.44</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="H5">
-        <v>79.47</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>76.98</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="G6">
-        <v>76.98</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="H6">
-        <v>76.98</v>
+        <v>87.11</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>62.3</v>
+        <v>79.44</v>
       </c>
       <c r="G7">
-        <v>76.12</v>
+        <v>79.44</v>
       </c>
       <c r="H7">
-        <v>80.92</v>
+        <v>79.44</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>73.66</v>
+        <v>73.36</v>
       </c>
       <c r="G8">
-        <v>76.04000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H8">
-        <v>78.75</v>
+        <v>87.11</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>57.07</v>
+        <v>62.07</v>
       </c>
       <c r="G9">
-        <v>75.92</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="H9">
-        <v>82.75</v>
+        <v>80.75</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>61.77</v>
+        <v>68.72</v>
       </c>
       <c r="G10">
-        <v>75.27</v>
+        <v>72.73</v>
       </c>
       <c r="H10">
-        <v>85.76000000000001</v>
+        <v>78.39</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>74.19</v>
+        <v>60.81</v>
       </c>
       <c r="G11">
-        <v>75.22</v>
+        <v>72.72</v>
       </c>
       <c r="H11">
-        <v>76.37</v>
+        <v>91.05</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>74.36</v>
+        <v>60.94</v>
       </c>
       <c r="G12">
-        <v>75.12</v>
+        <v>72.05</v>
       </c>
       <c r="H12">
-        <v>77.12</v>
+        <v>79.95</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>63.79</v>
+        <v>61.01</v>
       </c>
       <c r="G13">
-        <v>71.15000000000001</v>
+        <v>71.64</v>
       </c>
       <c r="H13">
-        <v>77.93000000000001</v>
+        <v>77.64</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>62.86</v>
+        <v>67.02</v>
       </c>
       <c r="G14">
-        <v>69.36</v>
+        <v>71.63</v>
       </c>
       <c r="H14">
-        <v>73.56</v>
+        <v>78.67</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1008,16 +1008,16 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>59.05</v>
+        <v>61.71</v>
       </c>
       <c r="G15">
-        <v>68.73999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="H15">
-        <v>75.16</v>
+        <v>78.84</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F16">
-        <v>58.59</v>
+        <v>55.37</v>
       </c>
       <c r="G16">
-        <v>68.48</v>
+        <v>69.69</v>
       </c>
       <c r="H16">
-        <v>83.05</v>
+        <v>76.95</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>58.59</v>
+        <v>61.09</v>
       </c>
       <c r="G17">
-        <v>67.70999999999999</v>
+        <v>68.92</v>
       </c>
       <c r="H17">
-        <v>83.05</v>
+        <v>76.97</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F18">
-        <v>63.3</v>
+        <v>62.36</v>
       </c>
       <c r="G18">
-        <v>67.34999999999999</v>
+        <v>67.94</v>
       </c>
       <c r="H18">
-        <v>69.95999999999999</v>
+        <v>76.87</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>60.72</v>
+        <v>60.1</v>
       </c>
       <c r="G19">
-        <v>67.16</v>
+        <v>67.8</v>
       </c>
       <c r="H19">
-        <v>72.92</v>
+        <v>71.67</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>55.18</v>
+        <v>58.58</v>
       </c>
       <c r="G20">
-        <v>67.03</v>
+        <v>67.67</v>
       </c>
       <c r="H20">
-        <v>74.28</v>
+        <v>78.34</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>58.19</v>
+        <v>59.68</v>
       </c>
       <c r="G21">
-        <v>66.76000000000001</v>
+        <v>65.78</v>
       </c>
       <c r="H21">
-        <v>80.92</v>
+        <v>73.47</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>59.26</v>
+        <v>53.24</v>
       </c>
       <c r="G22">
-        <v>66.06</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="H22">
-        <v>70.61</v>
+        <v>78.64</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>63.66</v>
+        <v>61.34</v>
       </c>
       <c r="G23">
-        <v>65.05</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="H23">
-        <v>66.44</v>
+        <v>74.08</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F24">
-        <v>59.8</v>
+        <v>49.5</v>
       </c>
       <c r="G24">
         <v>64.2</v>
       </c>
       <c r="H24">
-        <v>69.12</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F25">
-        <v>58.2</v>
+        <v>56.92</v>
       </c>
       <c r="G25">
-        <v>63.74</v>
+        <v>64.06</v>
       </c>
       <c r="H25">
-        <v>73.56999999999999</v>
+        <v>69.62</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>58.91</v>
+        <v>61.41</v>
       </c>
       <c r="G26">
-        <v>63.61</v>
+        <v>63.7</v>
       </c>
       <c r="H26">
-        <v>67.87</v>
+        <v>66.19</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F27">
-        <v>55.71</v>
+        <v>55.26</v>
       </c>
       <c r="G27">
-        <v>62.69</v>
+        <v>63.27</v>
       </c>
       <c r="H27">
-        <v>70.34999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="F28">
-        <v>57.37</v>
+        <v>54.14</v>
       </c>
       <c r="G28">
-        <v>62.63</v>
+        <v>62.83</v>
       </c>
       <c r="H28">
-        <v>69.02</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>57.83</v>
+        <v>62.36</v>
       </c>
       <c r="G29">
-        <v>62.14</v>
+        <v>62.36</v>
       </c>
       <c r="H29">
-        <v>64.79000000000001</v>
+        <v>62.36</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="G30">
-        <v>61.9</v>
+        <v>62.09</v>
       </c>
       <c r="H30">
-        <v>64.73999999999999</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>55.08</v>
+        <v>54.63</v>
       </c>
       <c r="G31">
-        <v>60.91</v>
+        <v>61.17</v>
       </c>
       <c r="H31">
-        <v>69.84999999999999</v>
+        <v>71.11</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>55.03</v>
+        <v>55.23</v>
       </c>
       <c r="G32">
-        <v>60.69</v>
+        <v>60.46</v>
       </c>
       <c r="H32">
-        <v>64.56999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>56.66</v>
+        <v>58.84</v>
       </c>
       <c r="G33">
-        <v>60.54</v>
+        <v>59.42</v>
       </c>
       <c r="H33">
-        <v>66.14</v>
+        <v>60</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,13 +1559,13 @@
         <v>3</v>
       </c>
       <c r="F34">
-        <v>56.2</v>
+        <v>53.31</v>
       </c>
       <c r="G34">
-        <v>58.4</v>
+        <v>56.99</v>
       </c>
       <c r="H34">
-        <v>59.97</v>
+        <v>61.31</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
+    <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
     <t>پارک ملي بختگان</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-10</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
+    <t>1405-06-11</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>136.98</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="G2">
-        <v>138.64</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="H2">
-        <v>140.65</v>
+        <v>102.39</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>94.41</v>
+        <v>86.8</v>
       </c>
       <c r="G3">
-        <v>105.87</v>
+        <v>88.17</v>
       </c>
       <c r="H3">
-        <v>120.54</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>80.3</v>
+        <v>81.05</v>
       </c>
       <c r="G4">
-        <v>92.8</v>
+        <v>83.94</v>
       </c>
       <c r="H4">
-        <v>109.4</v>
+        <v>87.89</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>74.16</v>
+        <v>77.31</v>
       </c>
       <c r="G5">
-        <v>81.45999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H5">
-        <v>83.40000000000001</v>
+        <v>87.95</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -747,13 +747,13 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>67.26000000000001</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="G6">
-        <v>80.79000000000001</v>
+        <v>81.11</v>
       </c>
       <c r="H6">
-        <v>87.11</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>79.44</v>
+        <v>70.45</v>
       </c>
       <c r="G7">
-        <v>79.44</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="H7">
-        <v>79.44</v>
+        <v>97.37</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>73.36</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="G8">
-        <v>78.95</v>
+        <v>78.02</v>
       </c>
       <c r="H8">
-        <v>87.11</v>
+        <v>82.28</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>62.07</v>
+        <v>70.7</v>
       </c>
       <c r="G9">
-        <v>73.79000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="H9">
-        <v>80.75</v>
+        <v>84.03</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>68.72</v>
+        <v>63.49</v>
       </c>
       <c r="G10">
-        <v>72.73</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="H10">
-        <v>78.39</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>60.81</v>
+        <v>72.88</v>
       </c>
       <c r="G11">
-        <v>72.72</v>
+        <v>76.89</v>
       </c>
       <c r="H11">
-        <v>91.05</v>
+        <v>79.81</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -921,13 +921,13 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>60.94</v>
+        <v>67.64</v>
       </c>
       <c r="G12">
-        <v>72.05</v>
+        <v>76.08</v>
       </c>
       <c r="H12">
-        <v>79.95</v>
+        <v>84.31</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>61.01</v>
+        <v>72.72</v>
       </c>
       <c r="G13">
-        <v>71.64</v>
+        <v>76.06</v>
       </c>
       <c r="H13">
-        <v>77.64</v>
+        <v>80.62</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,13 +979,13 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>67.02</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="G14">
-        <v>71.63</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="H14">
-        <v>78.67</v>
+        <v>81.22</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>61.71</v>
+        <v>72.11</v>
       </c>
       <c r="G15">
-        <v>70.48999999999999</v>
+        <v>75.58</v>
       </c>
       <c r="H15">
-        <v>78.84</v>
+        <v>77.58</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>55.37</v>
+        <v>70.44</v>
       </c>
       <c r="G16">
-        <v>69.69</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="H16">
-        <v>76.95</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>61.09</v>
+        <v>68.56</v>
       </c>
       <c r="G17">
-        <v>68.92</v>
+        <v>75.41</v>
       </c>
       <c r="H17">
-        <v>76.97</v>
+        <v>79.89</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>62.36</v>
+        <v>65.63</v>
       </c>
       <c r="G18">
-        <v>67.94</v>
+        <v>73.58</v>
       </c>
       <c r="H18">
-        <v>76.87</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>60.1</v>
+        <v>70.03</v>
       </c>
       <c r="G19">
-        <v>67.8</v>
+        <v>73.56</v>
       </c>
       <c r="H19">
-        <v>71.67</v>
+        <v>75.44</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>58.58</v>
+        <v>69.17</v>
       </c>
       <c r="G20">
-        <v>67.67</v>
+        <v>73.48</v>
       </c>
       <c r="H20">
-        <v>78.34</v>
+        <v>86.28</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>59.68</v>
+        <v>70.45</v>
       </c>
       <c r="G21">
-        <v>65.78</v>
+        <v>73.44</v>
       </c>
       <c r="H21">
-        <v>73.47</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F22">
-        <v>53.24</v>
+        <v>70.03</v>
       </c>
       <c r="G22">
-        <v>65.76000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="H22">
-        <v>78.64</v>
+        <v>74.78</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1240,16 +1240,16 @@
         <v>9</v>
       </c>
       <c r="F23">
-        <v>61.34</v>
+        <v>60.49</v>
       </c>
       <c r="G23">
-        <v>64.45999999999999</v>
+        <v>70.31</v>
       </c>
       <c r="H23">
-        <v>74.08</v>
+        <v>79.19</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="G24">
-        <v>64.2</v>
+        <v>70.3</v>
       </c>
       <c r="H24">
-        <v>77.81999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1298,16 +1298,16 @@
         <v>15</v>
       </c>
       <c r="F25">
-        <v>56.92</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="G25">
-        <v>64.06</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="H25">
-        <v>69.62</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>61.41</v>
+        <v>67.63</v>
       </c>
       <c r="G26">
-        <v>63.7</v>
+        <v>70.17</v>
       </c>
       <c r="H26">
-        <v>66.19</v>
+        <v>72.72</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="F27">
-        <v>55.26</v>
+        <v>60.04</v>
       </c>
       <c r="G27">
-        <v>63.27</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="H27">
-        <v>84.09999999999999</v>
+        <v>74.59</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="F28">
-        <v>54.14</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G28">
-        <v>62.83</v>
+        <v>68.47</v>
       </c>
       <c r="H28">
-        <v>84.09999999999999</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="F29">
-        <v>62.36</v>
+        <v>67.33</v>
       </c>
       <c r="G29">
-        <v>62.36</v>
+        <v>67.33</v>
       </c>
       <c r="H29">
-        <v>62.36</v>
+        <v>67.33</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>59.3</v>
+        <v>64.81</v>
       </c>
       <c r="G30">
-        <v>62.09</v>
+        <v>67.11</v>
       </c>
       <c r="H30">
-        <v>65.18000000000001</v>
+        <v>72.42</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>54.63</v>
+        <v>66.05</v>
       </c>
       <c r="G31">
-        <v>61.17</v>
+        <v>66.05</v>
       </c>
       <c r="H31">
-        <v>71.11</v>
+        <v>66.05</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="F32">
-        <v>55.23</v>
+        <v>55.11</v>
       </c>
       <c r="G32">
-        <v>60.46</v>
+        <v>65.87</v>
       </c>
       <c r="H32">
-        <v>64.65000000000001</v>
+        <v>75.58</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="F33">
-        <v>58.84</v>
+        <v>55.11</v>
       </c>
       <c r="G33">
-        <v>59.42</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="H33">
-        <v>60</v>
+        <v>75.58</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>53.31</v>
+        <v>60.05</v>
       </c>
       <c r="G34">
-        <v>56.99</v>
+        <v>63.79</v>
       </c>
       <c r="H34">
-        <v>61.31</v>
+        <v>71.16</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-11</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
+    <t>1405-06-12</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>79.15000000000001</v>
+        <v>93.52</v>
       </c>
       <c r="G2">
-        <v>92.48999999999999</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="H2">
-        <v>102.39</v>
+        <v>100.92</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>86.8</v>
+        <v>90.91</v>
       </c>
       <c r="G3">
-        <v>88.17</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="H3">
-        <v>89.43000000000001</v>
+        <v>93.61</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>81.05</v>
+        <v>66.08</v>
       </c>
       <c r="G4">
-        <v>83.94</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="H4">
-        <v>87.89</v>
+        <v>112.55</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>77.31</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="G5">
-        <v>82.59999999999999</v>
+        <v>85.11</v>
       </c>
       <c r="H5">
-        <v>87.95</v>
+        <v>87.64</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>78.06999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="G6">
-        <v>81.11</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="H6">
-        <v>85.26000000000001</v>
+        <v>91.88</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F7">
-        <v>70.45</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="G7">
-        <v>79.23999999999999</v>
+        <v>84.86</v>
       </c>
       <c r="H7">
-        <v>97.37</v>
+        <v>108.75</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F8">
-        <v>72.84999999999999</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="G8">
-        <v>78.02</v>
+        <v>84.31</v>
       </c>
       <c r="H8">
-        <v>82.28</v>
+        <v>108.75</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>70.7</v>
+        <v>78.36</v>
       </c>
       <c r="G9">
-        <v>77.56</v>
+        <v>83.91</v>
       </c>
       <c r="H9">
-        <v>84.03</v>
+        <v>86.78</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -863,13 +863,13 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>63.49</v>
+        <v>57.53</v>
       </c>
       <c r="G10">
-        <v>77.29000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="H10">
-        <v>96.51000000000001</v>
+        <v>112.39</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>72.88</v>
+        <v>81.89</v>
       </c>
       <c r="G11">
-        <v>76.89</v>
+        <v>82.38</v>
       </c>
       <c r="H11">
-        <v>79.81</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>67.64</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="G12">
-        <v>76.08</v>
+        <v>82.22</v>
       </c>
       <c r="H12">
-        <v>84.31</v>
+        <v>83.7</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>72.72</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="G13">
-        <v>76.06</v>
+        <v>81.72</v>
       </c>
       <c r="H13">
-        <v>80.62</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F14">
-        <v>65.73999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G14">
-        <v>75.70999999999999</v>
+        <v>80.92</v>
       </c>
       <c r="H14">
-        <v>81.22</v>
+        <v>89.77</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>72.11</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="G15">
-        <v>75.58</v>
+        <v>78.94</v>
       </c>
       <c r="H15">
-        <v>77.58</v>
+        <v>92.56</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>70.44</v>
+        <v>70.94</v>
       </c>
       <c r="G16">
-        <v>75.56999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="H16">
-        <v>80.59999999999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1066,13 +1066,13 @@
         <v>18</v>
       </c>
       <c r="F17">
-        <v>68.56</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="G17">
-        <v>75.41</v>
+        <v>78.45</v>
       </c>
       <c r="H17">
-        <v>79.89</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="I17" t="s">
         <v>48</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,13 +1095,13 @@
         <v>4</v>
       </c>
       <c r="F18">
-        <v>65.63</v>
+        <v>78.06</v>
       </c>
       <c r="G18">
-        <v>73.58</v>
+        <v>78.06</v>
       </c>
       <c r="H18">
-        <v>78.73999999999999</v>
+        <v>78.06</v>
       </c>
       <c r="I18" t="s">
         <v>48</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>70.03</v>
+        <v>73.97</v>
       </c>
       <c r="G19">
-        <v>73.56</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H19">
-        <v>75.44</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="I19" t="s">
         <v>48</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,13 +1153,13 @@
         <v>20</v>
       </c>
       <c r="F20">
-        <v>69.17</v>
+        <v>69.45</v>
       </c>
       <c r="G20">
-        <v>73.48</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="H20">
-        <v>86.28</v>
+        <v>84.66</v>
       </c>
       <c r="I20" t="s">
         <v>48</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>70.45</v>
+        <v>71.25</v>
       </c>
       <c r="G21">
-        <v>73.44</v>
+        <v>75.2</v>
       </c>
       <c r="H21">
-        <v>76.65000000000001</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="I21" t="s">
         <v>48</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>70.03</v>
+        <v>68.63</v>
       </c>
       <c r="G22">
-        <v>72.51000000000001</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="H22">
-        <v>74.78</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>48</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>60.49</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="G23">
-        <v>70.31</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="H23">
-        <v>79.19</v>
+        <v>80.05</v>
       </c>
       <c r="I23" t="s">
         <v>48</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>63.4</v>
+        <v>68.23</v>
       </c>
       <c r="G24">
-        <v>70.3</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="H24">
-        <v>81.09999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="I24" t="s">
         <v>48</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25">
-        <v>64.34999999999999</v>
+        <v>66.77</v>
       </c>
       <c r="G25">
-        <v>70.29000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="H25">
-        <v>75.23999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I25" t="s">
         <v>48</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>67.63</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="G26">
-        <v>70.17</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="H26">
-        <v>72.72</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="I26" t="s">
         <v>48</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>60.04</v>
+        <v>69.97</v>
       </c>
       <c r="G27">
-        <v>68.54000000000001</v>
+        <v>69.97</v>
       </c>
       <c r="H27">
-        <v>74.59</v>
+        <v>69.97</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>64.29000000000001</v>
+        <v>64.12</v>
       </c>
       <c r="G28">
-        <v>68.47</v>
+        <v>69.38</v>
       </c>
       <c r="H28">
-        <v>76.95999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>67.33</v>
+        <v>65.44</v>
       </c>
       <c r="G29">
-        <v>67.33</v>
+        <v>68.59</v>
       </c>
       <c r="H29">
-        <v>67.33</v>
+        <v>76.97</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>64.81</v>
+        <v>55.51</v>
       </c>
       <c r="G30">
-        <v>67.11</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H30">
-        <v>72.42</v>
+        <v>79.3</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>66.05</v>
+        <v>60.63</v>
       </c>
       <c r="G31">
-        <v>66.05</v>
+        <v>66.03</v>
       </c>
       <c r="H31">
-        <v>66.05</v>
+        <v>69.89</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="F32">
-        <v>55.11</v>
+        <v>62.35</v>
       </c>
       <c r="G32">
-        <v>65.87</v>
+        <v>64.22</v>
       </c>
       <c r="H32">
-        <v>75.58</v>
+        <v>65.81</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,13 +1527,13 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="F33">
-        <v>55.11</v>
+        <v>56.7</v>
       </c>
       <c r="G33">
-        <v>65.45999999999999</v>
+        <v>63.24</v>
       </c>
       <c r="H33">
         <v>75.58</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>60.05</v>
+        <v>56.97</v>
       </c>
       <c r="G34">
-        <v>63.79</v>
+        <v>62.05</v>
       </c>
       <c r="H34">
-        <v>71.16</v>
+        <v>65.62</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-12</t>
-  </si>
-  <si>
-    <t>2026-09-03</t>
+    <t>1405-06-13</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>93.52</v>
+        <v>77.31</v>
       </c>
       <c r="G2">
-        <v>98.43000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="H2">
-        <v>100.92</v>
+        <v>79.92</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>90.91</v>
+        <v>72.48</v>
       </c>
       <c r="G3">
-        <v>92.26000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="H3">
-        <v>93.61</v>
+        <v>81.45</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>66.08</v>
+        <v>73.11</v>
       </c>
       <c r="G4">
-        <v>88.51000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="H4">
-        <v>112.55</v>
+        <v>82.12</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>80.54000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="G5">
-        <v>85.11</v>
+        <v>76.05</v>
       </c>
       <c r="H5">
-        <v>87.64</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>78.73</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="G6">
-        <v>85.06999999999999</v>
+        <v>75.98</v>
       </c>
       <c r="H6">
-        <v>91.88</v>
+        <v>82.12</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>67.81999999999999</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="G7">
-        <v>84.86</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="H7">
-        <v>108.75</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>67.81999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="G8">
-        <v>84.31</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="H8">
-        <v>108.75</v>
+        <v>76.94</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>78.36</v>
+        <v>63.08</v>
       </c>
       <c r="G9">
-        <v>83.91</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="H9">
-        <v>86.78</v>
+        <v>76.78</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>57.53</v>
+        <v>63.77</v>
       </c>
       <c r="G10">
-        <v>83.56</v>
+        <v>71.11</v>
       </c>
       <c r="H10">
-        <v>112.39</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>81.89</v>
+        <v>62.55</v>
       </c>
       <c r="G11">
-        <v>82.38</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H11">
-        <v>82.73999999999999</v>
+        <v>75.84</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -921,13 +921,13 @@
         <v>5</v>
       </c>
       <c r="F12">
-        <v>81.51000000000001</v>
+        <v>67.28</v>
       </c>
       <c r="G12">
-        <v>82.22</v>
+        <v>70.17</v>
       </c>
       <c r="H12">
-        <v>83.7</v>
+        <v>74.08</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>75.73999999999999</v>
+        <v>69.88</v>
       </c>
       <c r="G13">
-        <v>81.72</v>
+        <v>69.88</v>
       </c>
       <c r="H13">
-        <v>91.65000000000001</v>
+        <v>69.88</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>71.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="G14">
-        <v>80.92</v>
+        <v>69.53</v>
       </c>
       <c r="H14">
-        <v>89.77</v>
+        <v>76.22</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>70.20999999999999</v>
+        <v>62.83</v>
       </c>
       <c r="G15">
-        <v>78.94</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H15">
-        <v>92.56</v>
+        <v>73.81</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F16">
-        <v>70.94</v>
+        <v>49.26</v>
       </c>
       <c r="G16">
-        <v>78.84</v>
+        <v>68.16</v>
       </c>
       <c r="H16">
-        <v>85.43000000000001</v>
+        <v>85.28</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F17">
-        <v>71.15000000000001</v>
+        <v>55.56</v>
       </c>
       <c r="G17">
-        <v>78.45</v>
+        <v>67.58</v>
       </c>
       <c r="H17">
-        <v>81.98999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>78.06</v>
+        <v>58.61</v>
       </c>
       <c r="G18">
-        <v>78.06</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="H18">
-        <v>78.06</v>
+        <v>77.28</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1124,16 +1124,16 @@
         <v>13</v>
       </c>
       <c r="F19">
-        <v>73.97</v>
+        <v>63.05</v>
       </c>
       <c r="G19">
-        <v>77.40000000000001</v>
+        <v>67.28</v>
       </c>
       <c r="H19">
-        <v>88.79000000000001</v>
+        <v>70.34</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>69.45</v>
+        <v>63.31</v>
       </c>
       <c r="G20">
-        <v>77.15000000000001</v>
+        <v>67.14</v>
       </c>
       <c r="H20">
-        <v>84.66</v>
+        <v>72.27</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>71.25</v>
+        <v>49.21</v>
       </c>
       <c r="G21">
-        <v>75.2</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="H21">
-        <v>79.65000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>68.63</v>
+        <v>61.57</v>
       </c>
       <c r="G22">
-        <v>74.84999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="H22">
-        <v>81.51000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>71.68000000000001</v>
+        <v>59.97</v>
       </c>
       <c r="G23">
-        <v>74.79000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="H23">
-        <v>80.05</v>
+        <v>69.83</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F24">
-        <v>68.23</v>
+        <v>52.69</v>
       </c>
       <c r="G24">
-        <v>73.70999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="H24">
-        <v>79.91</v>
+        <v>78.66</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>66.77</v>
+        <v>57.85</v>
       </c>
       <c r="G25">
-        <v>70.56999999999999</v>
+        <v>64.87</v>
       </c>
       <c r="H25">
-        <v>78.90000000000001</v>
+        <v>74.94</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F26">
-        <v>64.01000000000001</v>
+        <v>57.98</v>
       </c>
       <c r="G26">
-        <v>70.20999999999999</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="H26">
-        <v>76.04000000000001</v>
+        <v>78.36</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>69.97</v>
+        <v>61.81</v>
       </c>
       <c r="G27">
-        <v>69.97</v>
+        <v>64.66</v>
       </c>
       <c r="H27">
-        <v>69.97</v>
+        <v>68.14</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F28">
-        <v>64.12</v>
+        <v>52.69</v>
       </c>
       <c r="G28">
-        <v>69.38</v>
+        <v>64.58</v>
       </c>
       <c r="H28">
-        <v>73.81999999999999</v>
+        <v>78.66</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>65.44</v>
+        <v>60.03</v>
       </c>
       <c r="G29">
-        <v>68.59</v>
+        <v>63.55</v>
       </c>
       <c r="H29">
-        <v>76.97</v>
+        <v>70.02</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>55.51</v>
+        <v>57.12</v>
       </c>
       <c r="G30">
-        <v>67.65000000000001</v>
+        <v>63.19</v>
       </c>
       <c r="H30">
-        <v>79.3</v>
+        <v>69.88</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>60.63</v>
+        <v>56.84</v>
       </c>
       <c r="G31">
-        <v>66.03</v>
+        <v>62.48</v>
       </c>
       <c r="H31">
-        <v>69.89</v>
+        <v>68.84</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>62.35</v>
+        <v>57.51</v>
       </c>
       <c r="G32">
-        <v>64.22</v>
+        <v>59.27</v>
       </c>
       <c r="H32">
-        <v>65.81</v>
+        <v>61.02</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>56.7</v>
+        <v>51.86</v>
       </c>
       <c r="G33">
-        <v>63.24</v>
+        <v>59.09</v>
       </c>
       <c r="H33">
-        <v>75.58</v>
+        <v>64.97</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>56.97</v>
+        <v>53.73</v>
       </c>
       <c r="G34">
-        <v>62.05</v>
+        <v>53.73</v>
       </c>
       <c r="H34">
-        <v>65.62</v>
+        <v>53.73</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-13</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
+    <t>1405-06-14</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>77.31</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G2">
-        <v>79.2</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="H2">
-        <v>79.92</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>72.48</v>
+        <v>73.14</v>
       </c>
       <c r="G3">
-        <v>76.13</v>
+        <v>76.28</v>
       </c>
       <c r="H3">
-        <v>81.45</v>
+        <v>77.48</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>73.11</v>
+        <v>69.5</v>
       </c>
       <c r="G4">
-        <v>76.13</v>
+        <v>71.42</v>
       </c>
       <c r="H4">
-        <v>82.12</v>
+        <v>73.33</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>74.52</v>
+        <v>66.45</v>
       </c>
       <c r="G5">
-        <v>76.05</v>
+        <v>71.17</v>
       </c>
       <c r="H5">
-        <v>77.23999999999999</v>
+        <v>75.81</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>69.20999999999999</v>
+        <v>63.23</v>
       </c>
       <c r="G6">
-        <v>75.98</v>
+        <v>70.23</v>
       </c>
       <c r="H6">
-        <v>82.12</v>
+        <v>75.92</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F7">
-        <v>64.51000000000001</v>
+        <v>65.81</v>
       </c>
       <c r="G7">
-        <v>73.45999999999999</v>
+        <v>70.14</v>
       </c>
       <c r="H7">
-        <v>79.23999999999999</v>
+        <v>77.59</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -805,16 +805,16 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>66.45</v>
+        <v>62.59</v>
       </c>
       <c r="G8">
-        <v>72.18000000000001</v>
+        <v>69.58</v>
       </c>
       <c r="H8">
-        <v>76.94</v>
+        <v>75.58</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>63.08</v>
+        <v>58.97</v>
       </c>
       <c r="G9">
-        <v>71.51000000000001</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="H9">
-        <v>76.78</v>
+        <v>75.27</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>63.77</v>
+        <v>62.72</v>
       </c>
       <c r="G10">
-        <v>71.11</v>
+        <v>68.64</v>
       </c>
       <c r="H10">
-        <v>78.48999999999999</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>62.55</v>
+        <v>62.62</v>
       </c>
       <c r="G11">
-        <v>70.59999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="H11">
-        <v>75.84</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>67.28</v>
+        <v>65.69</v>
       </c>
       <c r="G12">
-        <v>70.17</v>
+        <v>67.25</v>
       </c>
       <c r="H12">
-        <v>74.08</v>
+        <v>68.38</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>69.88</v>
+        <v>63.55</v>
       </c>
       <c r="G13">
-        <v>69.88</v>
+        <v>66.83</v>
       </c>
       <c r="H13">
-        <v>69.88</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>64.5</v>
+        <v>63.12</v>
       </c>
       <c r="G14">
-        <v>69.53</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="H14">
-        <v>76.22</v>
+        <v>67.97</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>62.83</v>
+        <v>60.59</v>
       </c>
       <c r="G15">
-        <v>68.29000000000001</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="H15">
-        <v>73.81</v>
+        <v>67.94</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>49.26</v>
+        <v>58.52</v>
       </c>
       <c r="G16">
-        <v>68.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="H16">
-        <v>85.28</v>
+        <v>68.11</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F17">
-        <v>55.56</v>
+        <v>57.02</v>
       </c>
       <c r="G17">
-        <v>67.58</v>
+        <v>64.5</v>
       </c>
       <c r="H17">
-        <v>78.3</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>58.61</v>
+        <v>61.98</v>
       </c>
       <c r="G18">
-        <v>67.29000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H18">
-        <v>77.28</v>
+        <v>66.84</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>63.05</v>
+        <v>61.36</v>
       </c>
       <c r="G19">
-        <v>67.28</v>
+        <v>62.97</v>
       </c>
       <c r="H19">
-        <v>70.34</v>
+        <v>65.89</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>63.31</v>
+        <v>59.44</v>
       </c>
       <c r="G20">
-        <v>67.14</v>
+        <v>62.86</v>
       </c>
       <c r="H20">
-        <v>72.27</v>
+        <v>65.58</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>49.21</v>
+        <v>59.57</v>
       </c>
       <c r="G21">
-        <v>66.79000000000001</v>
+        <v>62.03</v>
       </c>
       <c r="H21">
-        <v>77.45999999999999</v>
+        <v>65.16</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>61.57</v>
+        <v>51.44</v>
       </c>
       <c r="G22">
-        <v>66.62</v>
+        <v>61.63</v>
       </c>
       <c r="H22">
-        <v>72.51000000000001</v>
+        <v>73.19</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>59.97</v>
+        <v>56.35</v>
       </c>
       <c r="G23">
-        <v>66.44</v>
+        <v>61.42</v>
       </c>
       <c r="H23">
-        <v>69.83</v>
+        <v>70.11</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>52.69</v>
+        <v>61.26</v>
       </c>
       <c r="G24">
-        <v>64.89</v>
+        <v>61.26</v>
       </c>
       <c r="H24">
-        <v>78.66</v>
+        <v>61.26</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>57.85</v>
+        <v>53.85</v>
       </c>
       <c r="G25">
-        <v>64.87</v>
+        <v>61.23</v>
       </c>
       <c r="H25">
-        <v>74.94</v>
+        <v>86.75</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>57.98</v>
+        <v>58.25</v>
       </c>
       <c r="G26">
-        <v>64.76000000000001</v>
+        <v>61.08</v>
       </c>
       <c r="H26">
-        <v>78.36</v>
+        <v>66.45</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="F27">
-        <v>61.81</v>
+        <v>54.3</v>
       </c>
       <c r="G27">
-        <v>64.66</v>
+        <v>61.04</v>
       </c>
       <c r="H27">
-        <v>68.14</v>
+        <v>70.72</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="F28">
-        <v>52.69</v>
+        <v>54.3</v>
       </c>
       <c r="G28">
-        <v>64.58</v>
+        <v>60.95</v>
       </c>
       <c r="H28">
-        <v>78.66</v>
+        <v>70.72</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>60.03</v>
+        <v>51.67</v>
       </c>
       <c r="G29">
-        <v>63.55</v>
+        <v>60.67</v>
       </c>
       <c r="H29">
-        <v>70.02</v>
+        <v>69.98</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>57.12</v>
+        <v>59.16</v>
       </c>
       <c r="G30">
-        <v>63.19</v>
+        <v>60.62</v>
       </c>
       <c r="H30">
-        <v>69.88</v>
+        <v>63.58</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>56.84</v>
+        <v>54.27</v>
       </c>
       <c r="G31">
-        <v>62.48</v>
+        <v>60.6</v>
       </c>
       <c r="H31">
-        <v>68.84</v>
+        <v>66.78</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>57.51</v>
+        <v>60.42</v>
       </c>
       <c r="G32">
-        <v>59.27</v>
+        <v>60.42</v>
       </c>
       <c r="H32">
-        <v>61.02</v>
+        <v>60.42</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>51.86</v>
+        <v>55.66</v>
       </c>
       <c r="G33">
-        <v>59.09</v>
+        <v>59.12</v>
       </c>
       <c r="H33">
-        <v>64.97</v>
+        <v>61.59</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>53.73</v>
+        <v>55.44</v>
       </c>
       <c r="G34">
-        <v>53.73</v>
+        <v>58.96</v>
       </c>
       <c r="H34">
-        <v>53.73</v>
+        <v>63.32</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-14</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
+    <t>1405-06-15</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>71.65000000000001</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="G2">
-        <v>78.20999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="H2">
-        <v>82.90000000000001</v>
+        <v>89.44</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>73.14</v>
+        <v>74.87</v>
       </c>
       <c r="G3">
-        <v>76.28</v>
+        <v>79.44</v>
       </c>
       <c r="H3">
-        <v>77.48</v>
+        <v>81.23</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="G4">
-        <v>71.42</v>
+        <v>77.3</v>
       </c>
       <c r="H4">
-        <v>73.33</v>
+        <v>80.83</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>66.45</v>
+        <v>73.34</v>
       </c>
       <c r="G5">
-        <v>71.17</v>
+        <v>76.58</v>
       </c>
       <c r="H5">
-        <v>75.81</v>
+        <v>80.08</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>63.23</v>
+        <v>72.67</v>
       </c>
       <c r="G6">
-        <v>70.23</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="H6">
-        <v>75.92</v>
+        <v>77.61</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>65.81</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="G7">
-        <v>70.14</v>
+        <v>72.97</v>
       </c>
       <c r="H7">
-        <v>77.59</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>62.59</v>
+        <v>71.66</v>
       </c>
       <c r="G8">
-        <v>69.58</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="H8">
-        <v>75.58</v>
+        <v>72.81</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>58.97</v>
+        <v>66.86</v>
       </c>
       <c r="G9">
-        <v>68.95999999999999</v>
+        <v>69.86</v>
       </c>
       <c r="H9">
-        <v>75.27</v>
+        <v>76.08</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>62.72</v>
+        <v>60.66</v>
       </c>
       <c r="G10">
-        <v>68.64</v>
+        <v>68.88</v>
       </c>
       <c r="H10">
-        <v>72.68000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>62.62</v>
+        <v>60.85</v>
       </c>
       <c r="G11">
-        <v>67.69</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H11">
-        <v>71.56999999999999</v>
+        <v>74.69</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>65.69</v>
+        <v>58.8</v>
       </c>
       <c r="G12">
-        <v>67.25</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="H12">
-        <v>68.38</v>
+        <v>76.52</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>63.55</v>
+        <v>61.54</v>
       </c>
       <c r="G13">
-        <v>66.83</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H13">
-        <v>70.95999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>63.12</v>
+        <v>56.99</v>
       </c>
       <c r="G14">
-        <v>65.45999999999999</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="H14">
-        <v>67.97</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>60.59</v>
+        <v>57.55</v>
       </c>
       <c r="G15">
-        <v>65.26000000000001</v>
+        <v>66.91</v>
       </c>
       <c r="H15">
-        <v>67.94</v>
+        <v>73.23</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F16">
-        <v>58.52</v>
+        <v>58.99</v>
       </c>
       <c r="G16">
-        <v>64.93000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H16">
-        <v>68.11</v>
+        <v>86.27</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>57.02</v>
+        <v>61.6</v>
       </c>
       <c r="G17">
-        <v>64.5</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H17">
-        <v>70.01000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="F18">
-        <v>61.98</v>
+        <v>55.6</v>
       </c>
       <c r="G18">
-        <v>64.40000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="H18">
-        <v>66.84</v>
+        <v>76.31</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>61.36</v>
+        <v>63.64</v>
       </c>
       <c r="G19">
-        <v>62.97</v>
+        <v>66.03</v>
       </c>
       <c r="H19">
-        <v>65.89</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>59.44</v>
+        <v>54.02</v>
       </c>
       <c r="G20">
-        <v>62.86</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="H20">
-        <v>65.58</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>59.57</v>
+        <v>55.72</v>
       </c>
       <c r="G21">
-        <v>62.03</v>
+        <v>65.59</v>
       </c>
       <c r="H21">
-        <v>65.16</v>
+        <v>76.2</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>51.44</v>
+        <v>61.55</v>
       </c>
       <c r="G22">
-        <v>61.63</v>
+        <v>64.69</v>
       </c>
       <c r="H22">
-        <v>73.19</v>
+        <v>68.64</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="F23">
-        <v>56.35</v>
+        <v>54.99</v>
       </c>
       <c r="G23">
-        <v>61.42</v>
+        <v>63.62</v>
       </c>
       <c r="H23">
-        <v>70.11</v>
+        <v>71.56</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>61.26</v>
+        <v>52.59</v>
       </c>
       <c r="G24">
-        <v>61.26</v>
+        <v>62.98</v>
       </c>
       <c r="H24">
-        <v>61.26</v>
+        <v>77.73</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="F25">
-        <v>53.85</v>
+        <v>51.94</v>
       </c>
       <c r="G25">
-        <v>61.23</v>
+        <v>62.89</v>
       </c>
       <c r="H25">
-        <v>86.75</v>
+        <v>73.05</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>58.25</v>
+        <v>57.59</v>
       </c>
       <c r="G26">
-        <v>61.08</v>
+        <v>62.44</v>
       </c>
       <c r="H26">
-        <v>66.45</v>
+        <v>67.23</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>54.3</v>
+        <v>61.98</v>
       </c>
       <c r="G27">
-        <v>61.04</v>
+        <v>61.98</v>
       </c>
       <c r="H27">
-        <v>70.72</v>
+        <v>61.98</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>54.3</v>
+        <v>54.81</v>
       </c>
       <c r="G28">
-        <v>60.95</v>
+        <v>61.53</v>
       </c>
       <c r="H28">
-        <v>70.72</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>51.67</v>
+        <v>56.5</v>
       </c>
       <c r="G29">
-        <v>60.67</v>
+        <v>60.26</v>
       </c>
       <c r="H29">
-        <v>69.98</v>
+        <v>61.59</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>59.16</v>
+        <v>54.07</v>
       </c>
       <c r="G30">
-        <v>60.62</v>
+        <v>59.52</v>
       </c>
       <c r="H30">
-        <v>63.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>54.27</v>
+        <v>55.56</v>
       </c>
       <c r="G31">
-        <v>60.6</v>
+        <v>58.98</v>
       </c>
       <c r="H31">
-        <v>66.78</v>
+        <v>62.22</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>60.42</v>
+        <v>57.01</v>
       </c>
       <c r="G32">
-        <v>60.42</v>
+        <v>58.56</v>
       </c>
       <c r="H32">
-        <v>60.42</v>
+        <v>62.27</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>55.66</v>
+        <v>53.95</v>
       </c>
       <c r="G33">
-        <v>59.12</v>
+        <v>53.95</v>
       </c>
       <c r="H33">
-        <v>61.59</v>
+        <v>53.95</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>55.44</v>
+        <v>47.68</v>
       </c>
       <c r="G34">
-        <v>58.96</v>
+        <v>52.08</v>
       </c>
       <c r="H34">
-        <v>63.32</v>
+        <v>54.71</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-15</t>
-  </si>
-  <si>
-    <t>2026-09-06</t>
+    <t>1405-06-16</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>75.29000000000001</v>
+        <v>83.16</v>
       </c>
       <c r="G2">
-        <v>82.38</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="H2">
-        <v>89.44</v>
+        <v>104.86</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>74.87</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="G3">
-        <v>79.44</v>
+        <v>89.98</v>
       </c>
       <c r="H3">
-        <v>81.23</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>73.5</v>
+        <v>83.98</v>
       </c>
       <c r="G4">
-        <v>77.3</v>
+        <v>88.23</v>
       </c>
       <c r="H4">
-        <v>80.83</v>
+        <v>92.36</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>73.34</v>
+        <v>83.03</v>
       </c>
       <c r="G5">
-        <v>76.58</v>
+        <v>85.88</v>
       </c>
       <c r="H5">
-        <v>80.08</v>
+        <v>88.73</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>72.67</v>
+        <v>79.5</v>
       </c>
       <c r="G6">
-        <v>75.65000000000001</v>
+        <v>85.64</v>
       </c>
       <c r="H6">
-        <v>77.61</v>
+        <v>89.17</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>67.26000000000001</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G7">
-        <v>72.97</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H7">
-        <v>79.06999999999999</v>
+        <v>89.88</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>71.66</v>
+        <v>84.37</v>
       </c>
       <c r="G8">
-        <v>72.23999999999999</v>
+        <v>84.86</v>
       </c>
       <c r="H8">
-        <v>72.81</v>
+        <v>85.47</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>66.86</v>
+        <v>74.34</v>
       </c>
       <c r="G9">
-        <v>69.86</v>
+        <v>84.52</v>
       </c>
       <c r="H9">
-        <v>76.08</v>
+        <v>89.64</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>60.66</v>
+        <v>79.48</v>
       </c>
       <c r="G10">
-        <v>68.88</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H10">
-        <v>76.48999999999999</v>
+        <v>88.13</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>60.85</v>
+        <v>83.77</v>
       </c>
       <c r="G11">
-        <v>68.56999999999999</v>
+        <v>83.77</v>
       </c>
       <c r="H11">
-        <v>74.69</v>
+        <v>83.77</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>58.8</v>
+        <v>68.16</v>
       </c>
       <c r="G12">
-        <v>68.20999999999999</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="H12">
-        <v>76.52</v>
+        <v>104.39</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>61.54</v>
+        <v>75.52</v>
       </c>
       <c r="G13">
-        <v>67.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H13">
-        <v>72.11</v>
+        <v>84.87</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="F14">
-        <v>56.99</v>
+        <v>61.49</v>
       </c>
       <c r="G14">
-        <v>67.45999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="H14">
-        <v>75.01000000000001</v>
+        <v>93.31</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F15">
-        <v>57.55</v>
+        <v>63.75</v>
       </c>
       <c r="G15">
-        <v>66.91</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H15">
-        <v>73.23</v>
+        <v>93.31</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F16">
-        <v>58.99</v>
+        <v>63.11</v>
       </c>
       <c r="G16">
-        <v>66.59999999999999</v>
+        <v>78.62</v>
       </c>
       <c r="H16">
-        <v>86.27</v>
+        <v>107.72</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>61.6</v>
+        <v>70.98</v>
       </c>
       <c r="G17">
-        <v>66.54000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="H17">
-        <v>68.56999999999999</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>55.6</v>
+        <v>74.33</v>
       </c>
       <c r="G18">
-        <v>66.03</v>
+        <v>78.34</v>
       </c>
       <c r="H18">
-        <v>76.31</v>
+        <v>82.75</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1121,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>63.64</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="G19">
-        <v>66.03</v>
+        <v>78.11</v>
       </c>
       <c r="H19">
-        <v>67.98999999999999</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="F20">
-        <v>54.02</v>
+        <v>70.34</v>
       </c>
       <c r="G20">
-        <v>65.98999999999999</v>
+        <v>77.12</v>
       </c>
       <c r="H20">
-        <v>76.01000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>55.72</v>
+        <v>67.28</v>
       </c>
       <c r="G21">
-        <v>65.59</v>
+        <v>75.14</v>
       </c>
       <c r="H21">
-        <v>76.2</v>
+        <v>83.78</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F22">
-        <v>61.55</v>
+        <v>69.48</v>
       </c>
       <c r="G22">
-        <v>64.69</v>
+        <v>74.19</v>
       </c>
       <c r="H22">
-        <v>68.64</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>54.99</v>
+        <v>72.2</v>
       </c>
       <c r="G23">
-        <v>63.62</v>
+        <v>74.16</v>
       </c>
       <c r="H23">
-        <v>71.56</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F24">
-        <v>52.59</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G24">
-        <v>62.98</v>
+        <v>73.63</v>
       </c>
       <c r="H24">
-        <v>77.73</v>
+        <v>78.84</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>51.94</v>
+        <v>65.2</v>
       </c>
       <c r="G25">
-        <v>62.89</v>
+        <v>73.52</v>
       </c>
       <c r="H25">
-        <v>73.05</v>
+        <v>82.06</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>57.59</v>
+        <v>58.98</v>
       </c>
       <c r="G26">
-        <v>62.44</v>
+        <v>72.38</v>
       </c>
       <c r="H26">
-        <v>67.23</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,19 +1353,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>61.98</v>
+        <v>67.09</v>
       </c>
       <c r="G27">
-        <v>61.98</v>
+        <v>70.92</v>
       </c>
       <c r="H27">
-        <v>61.98</v>
+        <v>76.73</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1382,19 +1382,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>54.81</v>
+        <v>59.09</v>
       </c>
       <c r="G28">
-        <v>61.53</v>
+        <v>70.91</v>
       </c>
       <c r="H28">
-        <v>72.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>56.5</v>
+        <v>59.09</v>
       </c>
       <c r="G29">
-        <v>60.26</v>
+        <v>69.77</v>
       </c>
       <c r="H29">
-        <v>61.59</v>
+        <v>84.23</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>54.07</v>
+        <v>54.8</v>
       </c>
       <c r="G30">
-        <v>59.52</v>
+        <v>69.16</v>
       </c>
       <c r="H30">
-        <v>66.65000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F31">
-        <v>55.56</v>
+        <v>64.55</v>
       </c>
       <c r="G31">
-        <v>58.98</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="H31">
-        <v>62.22</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>57.01</v>
+        <v>56.31</v>
       </c>
       <c r="G32">
-        <v>58.56</v>
+        <v>67.45</v>
       </c>
       <c r="H32">
-        <v>62.27</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>53.95</v>
+        <v>63.29</v>
       </c>
       <c r="G33">
-        <v>53.95</v>
+        <v>66.47</v>
       </c>
       <c r="H33">
-        <v>53.95</v>
+        <v>74.78</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>47.68</v>
+        <v>53.36</v>
       </c>
       <c r="G34">
-        <v>52.08</v>
+        <v>53.36</v>
       </c>
       <c r="H34">
-        <v>54.71</v>
+        <v>53.36</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-16</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
+    <t>1405-06-17</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>83.16</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="G2">
-        <v>96.54000000000001</v>
+        <v>102.99</v>
       </c>
       <c r="H2">
-        <v>104.86</v>
+        <v>118.89</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>87.34999999999999</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="G3">
-        <v>89.98</v>
+        <v>90.53</v>
       </c>
       <c r="H3">
-        <v>91.51000000000001</v>
+        <v>92.53</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>83.98</v>
+        <v>76.44</v>
       </c>
       <c r="G4">
-        <v>88.23</v>
+        <v>89.97</v>
       </c>
       <c r="H4">
-        <v>92.36</v>
+        <v>109.99</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>83.03</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="G5">
-        <v>85.88</v>
+        <v>77.28</v>
       </c>
       <c r="H5">
-        <v>88.73</v>
+        <v>81.5</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>79.5</v>
+        <v>67</v>
       </c>
       <c r="G6">
-        <v>85.64</v>
+        <v>76.63</v>
       </c>
       <c r="H6">
-        <v>89.17</v>
+        <v>89.91</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>75.98999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="G7">
-        <v>84.90000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="H7">
-        <v>89.88</v>
+        <v>81.94</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>84.37</v>
+        <v>67.91</v>
       </c>
       <c r="G8">
-        <v>84.86</v>
+        <v>74.7</v>
       </c>
       <c r="H8">
-        <v>85.47</v>
+        <v>76.52</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>74.34</v>
+        <v>62.17</v>
       </c>
       <c r="G9">
-        <v>84.52</v>
+        <v>70.92</v>
       </c>
       <c r="H9">
-        <v>89.64</v>
+        <v>79.45</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>79.48</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="G10">
-        <v>83.84999999999999</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H10">
-        <v>88.13</v>
+        <v>81.72</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>83.77</v>
+        <v>69.86</v>
       </c>
       <c r="G11">
-        <v>83.77</v>
+        <v>69.86</v>
       </c>
       <c r="H11">
-        <v>83.77</v>
+        <v>69.86</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>68.16</v>
+        <v>52.8</v>
       </c>
       <c r="G12">
-        <v>82.15000000000001</v>
+        <v>68.31</v>
       </c>
       <c r="H12">
-        <v>104.39</v>
+        <v>82.94</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>75.52</v>
+        <v>63.74</v>
       </c>
       <c r="G13">
-        <v>80</v>
+        <v>67.83</v>
       </c>
       <c r="H13">
-        <v>84.87</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="F14">
-        <v>61.49</v>
+        <v>63.54</v>
       </c>
       <c r="G14">
-        <v>79.44</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="H14">
-        <v>93.31</v>
+        <v>72.56</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>63.75</v>
+        <v>67.28</v>
       </c>
       <c r="G15">
-        <v>79.40000000000001</v>
+        <v>67.28</v>
       </c>
       <c r="H15">
-        <v>93.31</v>
+        <v>67.28</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>63.11</v>
+        <v>60.2</v>
       </c>
       <c r="G16">
-        <v>78.62</v>
+        <v>67.13</v>
       </c>
       <c r="H16">
-        <v>107.72</v>
+        <v>72.56</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>70.98</v>
+        <v>60.83</v>
       </c>
       <c r="G17">
-        <v>78.53</v>
+        <v>65.83</v>
       </c>
       <c r="H17">
-        <v>90.48999999999999</v>
+        <v>69.78</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>74.33</v>
+        <v>60.83</v>
       </c>
       <c r="G18">
-        <v>78.34</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="H18">
-        <v>82.75</v>
+        <v>72.37</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1121,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>73.06999999999999</v>
+        <v>55.99</v>
       </c>
       <c r="G19">
-        <v>78.11</v>
+        <v>64.2</v>
       </c>
       <c r="H19">
-        <v>83.70999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>70.34</v>
+        <v>60.19</v>
       </c>
       <c r="G20">
-        <v>77.12</v>
+        <v>63.64</v>
       </c>
       <c r="H20">
-        <v>87.7</v>
+        <v>67.84</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>67.28</v>
+        <v>62.17</v>
       </c>
       <c r="G21">
-        <v>75.14</v>
+        <v>63.48</v>
       </c>
       <c r="H21">
-        <v>83.78</v>
+        <v>64.44</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="F22">
-        <v>69.48</v>
+        <v>50.75</v>
       </c>
       <c r="G22">
-        <v>74.19</v>
+        <v>62.23</v>
       </c>
       <c r="H22">
-        <v>79.68000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>72.2</v>
+        <v>54.15</v>
       </c>
       <c r="G23">
-        <v>74.16</v>
+        <v>62.11</v>
       </c>
       <c r="H23">
-        <v>76.70999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F24">
-        <v>69.31999999999999</v>
+        <v>53.84</v>
       </c>
       <c r="G24">
-        <v>73.63</v>
+        <v>61.64</v>
       </c>
       <c r="H24">
-        <v>78.84</v>
+        <v>71.5</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F25">
-        <v>65.2</v>
+        <v>54.76</v>
       </c>
       <c r="G25">
-        <v>73.52</v>
+        <v>61.2</v>
       </c>
       <c r="H25">
-        <v>82.06</v>
+        <v>66.2</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="F26">
-        <v>58.98</v>
+        <v>51.25</v>
       </c>
       <c r="G26">
-        <v>72.38</v>
+        <v>61.08</v>
       </c>
       <c r="H26">
-        <v>78.34999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1353,19 +1353,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>67.09</v>
+        <v>55.66</v>
       </c>
       <c r="G27">
-        <v>70.92</v>
+        <v>61</v>
       </c>
       <c r="H27">
-        <v>76.73</v>
+        <v>65.72</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,19 +1382,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>59.09</v>
+        <v>56.28</v>
       </c>
       <c r="G28">
-        <v>70.91</v>
+        <v>60.43</v>
       </c>
       <c r="H28">
-        <v>76.90000000000001</v>
+        <v>64.58</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>59.09</v>
+        <v>57.74</v>
       </c>
       <c r="G29">
-        <v>69.77</v>
+        <v>59.89</v>
       </c>
       <c r="H29">
-        <v>84.23</v>
+        <v>60.86</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>54.8</v>
+        <v>52.6</v>
       </c>
       <c r="G30">
-        <v>69.16</v>
+        <v>59.76</v>
       </c>
       <c r="H30">
-        <v>84.7</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F31">
-        <v>64.55</v>
+        <v>55.6</v>
       </c>
       <c r="G31">
-        <v>68.51000000000001</v>
+        <v>58.49</v>
       </c>
       <c r="H31">
-        <v>75.29000000000001</v>
+        <v>62.48</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F32">
-        <v>56.31</v>
+        <v>52.15</v>
       </c>
       <c r="G32">
-        <v>67.45</v>
+        <v>57.6</v>
       </c>
       <c r="H32">
-        <v>74.18000000000001</v>
+        <v>66.56</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>63.29</v>
+        <v>57.45</v>
       </c>
       <c r="G33">
-        <v>66.47</v>
+        <v>57.45</v>
       </c>
       <c r="H33">
-        <v>74.78</v>
+        <v>57.45</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>53.36</v>
+        <v>54.28</v>
       </c>
       <c r="G34">
-        <v>53.36</v>
+        <v>56.39</v>
       </c>
       <c r="H34">
-        <v>53.36</v>
+        <v>62.01</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-17</t>
-  </si>
-  <si>
-    <t>2026-09-08</t>
+    <t>1405-06-18</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>82.43000000000001</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="G2">
-        <v>102.99</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="H2">
-        <v>118.89</v>
+        <v>105.69</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>87.73999999999999</v>
+        <v>83.11</v>
       </c>
       <c r="G3">
-        <v>90.53</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H3">
-        <v>92.53</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>76.44</v>
+        <v>85.33</v>
       </c>
       <c r="G4">
-        <v>89.97</v>
+        <v>87.03</v>
       </c>
       <c r="H4">
-        <v>109.99</v>
+        <v>88.11</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>70.68000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="G5">
-        <v>77.28</v>
+        <v>85.42</v>
       </c>
       <c r="H5">
-        <v>81.5</v>
+        <v>90.27</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>67</v>
+        <v>79.89</v>
       </c>
       <c r="G6">
-        <v>76.63</v>
+        <v>84.73</v>
       </c>
       <c r="H6">
-        <v>89.91</v>
+        <v>88.95</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>68.75</v>
+        <v>79</v>
       </c>
       <c r="G7">
-        <v>75.81</v>
+        <v>83.16</v>
       </c>
       <c r="H7">
-        <v>81.94</v>
+        <v>91.11</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>67.91</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="G8">
-        <v>74.7</v>
+        <v>82.28</v>
       </c>
       <c r="H8">
-        <v>76.52</v>
+        <v>93.73</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>62.17</v>
+        <v>76.55</v>
       </c>
       <c r="G9">
-        <v>70.92</v>
+        <v>82.2</v>
       </c>
       <c r="H9">
-        <v>79.45</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>64.98999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="G10">
-        <v>69.98999999999999</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="H10">
-        <v>81.72</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>69.86</v>
+        <v>75.67</v>
       </c>
       <c r="G11">
-        <v>69.86</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="H11">
-        <v>69.86</v>
+        <v>82.88</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>52.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G12">
-        <v>68.31</v>
+        <v>77.48</v>
       </c>
       <c r="H12">
-        <v>82.94</v>
+        <v>94.42</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>63.74</v>
+        <v>63.42</v>
       </c>
       <c r="G13">
-        <v>67.83</v>
+        <v>74.92</v>
       </c>
       <c r="H13">
-        <v>71.73999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="F14">
-        <v>63.54</v>
+        <v>67.14</v>
       </c>
       <c r="G14">
-        <v>67.54000000000001</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="H14">
-        <v>72.56</v>
+        <v>85.14</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>67.28</v>
+        <v>66.11</v>
       </c>
       <c r="G15">
-        <v>67.28</v>
+        <v>73</v>
       </c>
       <c r="H15">
-        <v>67.28</v>
+        <v>80.33</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>60.2</v>
+        <v>58.88</v>
       </c>
       <c r="G16">
-        <v>67.13</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="H16">
-        <v>72.56</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>60.83</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="G17">
-        <v>65.83</v>
+        <v>71.95</v>
       </c>
       <c r="H17">
-        <v>69.78</v>
+        <v>77.27</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>60.83</v>
+        <v>59.69</v>
       </c>
       <c r="G18">
-        <v>65.68000000000001</v>
+        <v>71.37</v>
       </c>
       <c r="H18">
-        <v>72.37</v>
+        <v>79.31</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1121,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19">
-        <v>55.99</v>
+        <v>67.05</v>
       </c>
       <c r="G19">
-        <v>64.2</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="H19">
-        <v>70.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>60.19</v>
+        <v>67.86</v>
       </c>
       <c r="G20">
-        <v>63.64</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H20">
-        <v>67.84</v>
+        <v>74.41</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="F21">
-        <v>62.17</v>
+        <v>57.69</v>
       </c>
       <c r="G21">
-        <v>63.48</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H21">
-        <v>64.44</v>
+        <v>81.16</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F22">
-        <v>50.75</v>
+        <v>60.21</v>
       </c>
       <c r="G22">
-        <v>62.23</v>
+        <v>70.23</v>
       </c>
       <c r="H22">
-        <v>70.40000000000001</v>
+        <v>78.84</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F23">
-        <v>54.15</v>
+        <v>61.07</v>
       </c>
       <c r="G23">
-        <v>62.11</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="H23">
-        <v>69.05</v>
+        <v>79.31</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>53.84</v>
+        <v>64.81</v>
       </c>
       <c r="G24">
-        <v>61.64</v>
+        <v>69.28</v>
       </c>
       <c r="H24">
-        <v>71.5</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>54.76</v>
+        <v>54.55</v>
       </c>
       <c r="G25">
-        <v>61.2</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="H25">
-        <v>66.2</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>51.25</v>
+        <v>63.52</v>
       </c>
       <c r="G26">
-        <v>61.08</v>
+        <v>68.55</v>
       </c>
       <c r="H26">
-        <v>71.5</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F27">
-        <v>55.66</v>
+        <v>64.62</v>
       </c>
       <c r="G27">
-        <v>61</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H27">
-        <v>65.72</v>
+        <v>75.83</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>56.28</v>
+        <v>60.32</v>
       </c>
       <c r="G28">
-        <v>60.43</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H28">
-        <v>64.58</v>
+        <v>78.38</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>57.74</v>
+        <v>55.66</v>
       </c>
       <c r="G29">
-        <v>59.89</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H29">
-        <v>60.86</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>52.6</v>
+        <v>61.86</v>
       </c>
       <c r="G30">
-        <v>59.76</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="H30">
-        <v>75.48999999999999</v>
+        <v>76.23</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>55.6</v>
+        <v>58.59</v>
       </c>
       <c r="G31">
-        <v>58.49</v>
+        <v>65.83</v>
       </c>
       <c r="H31">
-        <v>62.48</v>
+        <v>77.38</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1501,13 +1501,13 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>52.15</v>
+        <v>57.63</v>
       </c>
       <c r="G32">
-        <v>57.6</v>
+        <v>63.28</v>
       </c>
       <c r="H32">
-        <v>66.56</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1530,13 +1530,13 @@
         <v>4</v>
       </c>
       <c r="F33">
-        <v>57.45</v>
+        <v>62.72</v>
       </c>
       <c r="G33">
-        <v>57.45</v>
+        <v>62.72</v>
       </c>
       <c r="H33">
-        <v>57.45</v>
+        <v>62.72</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>54.28</v>
+        <v>53.9</v>
       </c>
       <c r="G34">
-        <v>56.39</v>
+        <v>53.9</v>
       </c>
       <c r="H34">
-        <v>62.01</v>
+        <v>53.9</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-18</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
+    <t>1405-06-19</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>77.73999999999999</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="G2">
-        <v>94.23999999999999</v>
+        <v>105.73</v>
       </c>
       <c r="H2">
-        <v>105.69</v>
+        <v>113.34</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>83.11</v>
+        <v>92.37</v>
       </c>
       <c r="G3">
-        <v>91.54000000000001</v>
+        <v>101.11</v>
       </c>
       <c r="H3">
-        <v>97.43000000000001</v>
+        <v>109.46</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,13 +689,13 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>85.33</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="G4">
-        <v>87.03</v>
+        <v>100.09</v>
       </c>
       <c r="H4">
-        <v>88.11</v>
+        <v>101.44</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>78.23999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="G5">
-        <v>85.42</v>
+        <v>99.42</v>
       </c>
       <c r="H5">
-        <v>90.27</v>
+        <v>105.59</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>79.89</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G6">
-        <v>84.73</v>
+        <v>96.77</v>
       </c>
       <c r="H6">
-        <v>88.95</v>
+        <v>97.97</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>79</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="G7">
-        <v>83.16</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="H7">
-        <v>91.11</v>
+        <v>105.88</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>76.04000000000001</v>
+        <v>84.31</v>
       </c>
       <c r="G8">
-        <v>82.28</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="H8">
-        <v>93.73</v>
+        <v>109.11</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>76.55</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="G9">
-        <v>82.2</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="H9">
-        <v>89.51000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>64.84</v>
+        <v>82.03</v>
       </c>
       <c r="G10">
-        <v>81.93000000000001</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="H10">
-        <v>95.56999999999999</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F11">
-        <v>75.67</v>
+        <v>75.58</v>
       </c>
       <c r="G11">
-        <v>79.93000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="H11">
-        <v>82.88</v>
+        <v>100.89</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="F12">
-        <v>69.40000000000001</v>
+        <v>69.39</v>
       </c>
       <c r="G12">
-        <v>77.48</v>
+        <v>87.87</v>
       </c>
       <c r="H12">
-        <v>94.42</v>
+        <v>100.89</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -950,13 +950,13 @@
         <v>23</v>
       </c>
       <c r="F13">
-        <v>63.42</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="G13">
-        <v>74.92</v>
+        <v>86.37</v>
       </c>
       <c r="H13">
-        <v>78.8</v>
+        <v>91.39</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="F14">
-        <v>67.14</v>
+        <v>74.75</v>
       </c>
       <c r="G14">
-        <v>74.26000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="H14">
-        <v>85.14</v>
+        <v>98.17</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>66.11</v>
+        <v>71.41</v>
       </c>
       <c r="G15">
-        <v>73</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H15">
-        <v>80.33</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>58.88</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="G16">
-        <v>72.73999999999999</v>
+        <v>79.64</v>
       </c>
       <c r="H16">
-        <v>79.81999999999999</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>67.20999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="G17">
-        <v>71.95</v>
+        <v>79.48</v>
       </c>
       <c r="H17">
-        <v>77.27</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="I17" t="s">
         <v>48</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>59.69</v>
+        <v>78.19</v>
       </c>
       <c r="G18">
-        <v>71.37</v>
+        <v>79.05</v>
       </c>
       <c r="H18">
-        <v>79.31</v>
+        <v>79.92</v>
       </c>
       <c r="I18" t="s">
         <v>48</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>67.05</v>
+        <v>75.52</v>
       </c>
       <c r="G19">
-        <v>70.98999999999999</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="H19">
-        <v>74.5</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="I19" t="s">
         <v>48</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F20">
-        <v>67.86</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G20">
-        <v>70.40000000000001</v>
+        <v>77.81</v>
       </c>
       <c r="H20">
-        <v>74.41</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I20" t="s">
         <v>48</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>57.69</v>
+        <v>62.1</v>
       </c>
       <c r="G21">
-        <v>70.40000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H21">
-        <v>81.16</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="I21" t="s">
         <v>48</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>60.21</v>
+        <v>63.3</v>
       </c>
       <c r="G22">
-        <v>70.23</v>
+        <v>73.06</v>
       </c>
       <c r="H22">
-        <v>78.84</v>
+        <v>82.77</v>
       </c>
       <c r="I22" t="s">
         <v>48</v>
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>61.07</v>
+        <v>62.1</v>
       </c>
       <c r="G23">
-        <v>69.70999999999999</v>
+        <v>72.27</v>
       </c>
       <c r="H23">
-        <v>79.31</v>
+        <v>82.91</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>64.81</v>
+        <v>68.25</v>
       </c>
       <c r="G24">
-        <v>69.28</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="H24">
-        <v>70.95999999999999</v>
+        <v>82.44</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>54.55</v>
+        <v>61.98</v>
       </c>
       <c r="G25">
-        <v>68.95999999999999</v>
+        <v>71.39</v>
       </c>
       <c r="H25">
-        <v>82.73999999999999</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1327,16 +1327,16 @@
         <v>2</v>
       </c>
       <c r="F26">
-        <v>63.52</v>
+        <v>70.09</v>
       </c>
       <c r="G26">
-        <v>68.55</v>
+        <v>70.09</v>
       </c>
       <c r="H26">
-        <v>73.56999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>64.62</v>
+        <v>65.73</v>
       </c>
       <c r="G27">
-        <v>68.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="H27">
-        <v>75.83</v>
+        <v>76.36</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>60.32</v>
+        <v>60.42</v>
       </c>
       <c r="G28">
-        <v>68.09999999999999</v>
+        <v>65.17</v>
       </c>
       <c r="H28">
-        <v>78.38</v>
+        <v>71.88</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="F29">
-        <v>55.66</v>
+        <v>49.46</v>
       </c>
       <c r="G29">
-        <v>67.73999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="H29">
-        <v>78.95999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F30">
-        <v>61.86</v>
+        <v>50.48</v>
       </c>
       <c r="G30">
-        <v>67.70999999999999</v>
+        <v>61.78</v>
       </c>
       <c r="H30">
-        <v>76.23</v>
+        <v>74.66</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>58.59</v>
+        <v>52.62</v>
       </c>
       <c r="G31">
-        <v>65.83</v>
+        <v>61.28</v>
       </c>
       <c r="H31">
-        <v>77.38</v>
+        <v>72.87</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>57.63</v>
+        <v>55.7</v>
       </c>
       <c r="G32">
-        <v>63.28</v>
+        <v>59.32</v>
       </c>
       <c r="H32">
-        <v>74.26000000000001</v>
+        <v>63.18</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,13 +1530,13 @@
         <v>4</v>
       </c>
       <c r="F33">
-        <v>62.72</v>
+        <v>54.08</v>
       </c>
       <c r="G33">
-        <v>62.72</v>
+        <v>58.7</v>
       </c>
       <c r="H33">
-        <v>62.72</v>
+        <v>62.46</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>53.9</v>
+        <v>54.67</v>
       </c>
       <c r="G34">
-        <v>53.9</v>
+        <v>57.7</v>
       </c>
       <c r="H34">
-        <v>53.9</v>
+        <v>61.98</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-19</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
+    <t>1405-06-20</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>99.76000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G2">
-        <v>105.73</v>
+        <v>88.48</v>
       </c>
       <c r="H2">
-        <v>113.34</v>
+        <v>107.66</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>92.37</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G3">
-        <v>101.11</v>
+        <v>86.61</v>
       </c>
       <c r="H3">
-        <v>109.46</v>
+        <v>88.87</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>98.56999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="G4">
-        <v>100.09</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H4">
-        <v>101.44</v>
+        <v>80.89</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>85.25</v>
+        <v>71.48</v>
       </c>
       <c r="G5">
-        <v>99.42</v>
+        <v>76.64</v>
       </c>
       <c r="H5">
-        <v>105.59</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>95.81999999999999</v>
+        <v>73.08</v>
       </c>
       <c r="G6">
-        <v>96.77</v>
+        <v>75.87</v>
       </c>
       <c r="H6">
-        <v>97.97</v>
+        <v>79.72</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>77.01000000000001</v>
+        <v>74.33</v>
       </c>
       <c r="G7">
-        <v>93.81999999999999</v>
+        <v>75.64</v>
       </c>
       <c r="H7">
-        <v>105.88</v>
+        <v>76.31</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>84.31</v>
+        <v>62.78</v>
       </c>
       <c r="G8">
-        <v>93.29000000000001</v>
+        <v>74.34</v>
       </c>
       <c r="H8">
-        <v>109.11</v>
+        <v>91.28</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>92.93000000000001</v>
+        <v>71.53</v>
       </c>
       <c r="G9">
-        <v>92.93000000000001</v>
+        <v>73.86</v>
       </c>
       <c r="H9">
-        <v>92.93000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>82.03</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="G10">
-        <v>89.84999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="H10">
-        <v>96.48999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>75.58</v>
+        <v>67.48</v>
       </c>
       <c r="G11">
-        <v>88.89</v>
+        <v>71.94</v>
       </c>
       <c r="H11">
-        <v>100.89</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="F12">
-        <v>69.39</v>
+        <v>61.07</v>
       </c>
       <c r="G12">
-        <v>87.87</v>
+        <v>71.48</v>
       </c>
       <c r="H12">
-        <v>100.89</v>
+        <v>80.63</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>77.45999999999999</v>
+        <v>66.28</v>
       </c>
       <c r="G13">
-        <v>86.37</v>
+        <v>70.84</v>
       </c>
       <c r="H13">
-        <v>91.39</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>74.75</v>
+        <v>63.39</v>
       </c>
       <c r="G14">
-        <v>82.67</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="H14">
-        <v>98.17</v>
+        <v>110.3</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>71.41</v>
+        <v>68.89</v>
       </c>
       <c r="G15">
-        <v>80.59999999999999</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="H15">
-        <v>87.70999999999999</v>
+        <v>73.91</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>72.45999999999999</v>
+        <v>67</v>
       </c>
       <c r="G16">
-        <v>79.64</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="H16">
-        <v>88.65000000000001</v>
+        <v>78.73</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>73.2</v>
+        <v>63.45</v>
       </c>
       <c r="G17">
-        <v>79.48</v>
+        <v>70.63</v>
       </c>
       <c r="H17">
-        <v>84.23999999999999</v>
+        <v>79.84</v>
       </c>
       <c r="I17" t="s">
         <v>48</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>78.19</v>
+        <v>60.08</v>
       </c>
       <c r="G18">
-        <v>79.05</v>
+        <v>70.27</v>
       </c>
       <c r="H18">
-        <v>79.92</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="I18" t="s">
         <v>48</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>75.52</v>
+        <v>61.64</v>
       </c>
       <c r="G19">
-        <v>78.34999999999999</v>
+        <v>70.14</v>
       </c>
       <c r="H19">
-        <v>81.15000000000001</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="I19" t="s">
         <v>48</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>71.84999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="G20">
-        <v>77.81</v>
+        <v>69.23</v>
       </c>
       <c r="H20">
-        <v>82.01000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>62.1</v>
+        <v>58.83</v>
       </c>
       <c r="G21">
-        <v>73.53</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="H21">
-        <v>85.76000000000001</v>
+        <v>73.63</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>63.3</v>
+        <v>57.83</v>
       </c>
       <c r="G22">
-        <v>73.06</v>
+        <v>67.25</v>
       </c>
       <c r="H22">
-        <v>82.77</v>
+        <v>74.58</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F23">
-        <v>62.1</v>
+        <v>54.12</v>
       </c>
       <c r="G23">
-        <v>72.27</v>
+        <v>67.23</v>
       </c>
       <c r="H23">
-        <v>82.91</v>
+        <v>79.38</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>68.25</v>
+        <v>57.08</v>
       </c>
       <c r="G24">
-        <v>71.93000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="H24">
-        <v>82.44</v>
+        <v>77.16</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="F25">
-        <v>61.98</v>
+        <v>54.12</v>
       </c>
       <c r="G25">
-        <v>71.39</v>
+        <v>65.97</v>
       </c>
       <c r="H25">
-        <v>83.34999999999999</v>
+        <v>79.38</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F26">
-        <v>70.09</v>
+        <v>59.35</v>
       </c>
       <c r="G26">
-        <v>70.09</v>
+        <v>65.36</v>
       </c>
       <c r="H26">
-        <v>70.09</v>
+        <v>71.56</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>65.73</v>
+        <v>59.72</v>
       </c>
       <c r="G27">
-        <v>69.17</v>
+        <v>65.13</v>
       </c>
       <c r="H27">
-        <v>76.36</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F28">
-        <v>60.42</v>
+        <v>59.81</v>
       </c>
       <c r="G28">
-        <v>65.17</v>
+        <v>65.02</v>
       </c>
       <c r="H28">
-        <v>71.88</v>
+        <v>69.23</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>49.46</v>
+        <v>58.77</v>
       </c>
       <c r="G29">
-        <v>64.84</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="H29">
-        <v>77.14</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>50.48</v>
+        <v>59.92</v>
       </c>
       <c r="G30">
-        <v>61.78</v>
+        <v>63.32</v>
       </c>
       <c r="H30">
-        <v>74.66</v>
+        <v>68.94</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>52.62</v>
+        <v>55.17</v>
       </c>
       <c r="G31">
-        <v>61.28</v>
+        <v>63.28</v>
       </c>
       <c r="H31">
-        <v>72.87</v>
+        <v>70.91</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>55.7</v>
+        <v>59.29</v>
       </c>
       <c r="G32">
-        <v>59.32</v>
+        <v>62.99</v>
       </c>
       <c r="H32">
-        <v>63.18</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F33">
-        <v>54.08</v>
+        <v>54.34</v>
       </c>
       <c r="G33">
-        <v>58.7</v>
+        <v>60</v>
       </c>
       <c r="H33">
-        <v>62.46</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>54.67</v>
+        <v>55.42</v>
       </c>
       <c r="G34">
-        <v>57.7</v>
+        <v>55.42</v>
       </c>
       <c r="H34">
-        <v>61.98</v>
+        <v>55.42</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
+    <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-20</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
+    <t>1405-06-21</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>74.40000000000001</v>
+        <v>86.31</v>
       </c>
       <c r="G2">
-        <v>88.48</v>
+        <v>101.63</v>
       </c>
       <c r="H2">
-        <v>107.66</v>
+        <v>115.5</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>85.04000000000001</v>
+        <v>88.91</v>
       </c>
       <c r="G3">
-        <v>86.61</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H3">
-        <v>88.87</v>
+        <v>103.06</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>75.25</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G4">
-        <v>78.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H4">
-        <v>80.89</v>
+        <v>116.29</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>71.48</v>
+        <v>86.31</v>
       </c>
       <c r="G5">
-        <v>76.64</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="H5">
-        <v>83.65000000000001</v>
+        <v>105.03</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>73.08</v>
+        <v>92.61</v>
       </c>
       <c r="G6">
-        <v>75.87</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="H6">
-        <v>79.72</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>74.33</v>
+        <v>88.63</v>
       </c>
       <c r="G7">
-        <v>75.64</v>
+        <v>91.44</v>
       </c>
       <c r="H7">
-        <v>76.31</v>
+        <v>93.36</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>62.78</v>
+        <v>71.97</v>
       </c>
       <c r="G8">
-        <v>74.34</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="H8">
-        <v>91.28</v>
+        <v>97.12</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>71.53</v>
+        <v>63.78</v>
       </c>
       <c r="G9">
-        <v>73.86</v>
+        <v>84.37</v>
       </c>
       <c r="H9">
-        <v>79.41</v>
+        <v>94.94</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>67.79000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G10">
-        <v>73.12</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="H10">
-        <v>77.7</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>67.48</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="G11">
-        <v>71.94</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="H11">
-        <v>75.15000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>61.07</v>
+        <v>80.25</v>
       </c>
       <c r="G12">
-        <v>71.48</v>
+        <v>80.25</v>
       </c>
       <c r="H12">
-        <v>80.63</v>
+        <v>80.25</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>66.28</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G13">
-        <v>70.84</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H13">
-        <v>73</v>
+        <v>90.8</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F14">
-        <v>63.39</v>
+        <v>69.86</v>
       </c>
       <c r="G14">
-        <v>70.81999999999999</v>
+        <v>78.38</v>
       </c>
       <c r="H14">
-        <v>110.3</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>68.89</v>
+        <v>70.27</v>
       </c>
       <c r="G15">
-        <v>70.79000000000001</v>
+        <v>77.73</v>
       </c>
       <c r="H15">
-        <v>73.91</v>
+        <v>86.83</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>67</v>
+        <v>69.73</v>
       </c>
       <c r="G16">
-        <v>70.76000000000001</v>
+        <v>77.73</v>
       </c>
       <c r="H16">
-        <v>78.73</v>
+        <v>83.72</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>63.45</v>
+        <v>71.53</v>
       </c>
       <c r="G17">
-        <v>70.63</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H17">
-        <v>79.84</v>
+        <v>79.86</v>
       </c>
       <c r="I17" t="s">
         <v>48</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>60.08</v>
+        <v>66.42</v>
       </c>
       <c r="G18">
-        <v>70.27</v>
+        <v>76.34</v>
       </c>
       <c r="H18">
-        <v>78.73999999999999</v>
+        <v>86.42</v>
       </c>
       <c r="I18" t="s">
         <v>48</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>61.64</v>
+        <v>75.92</v>
       </c>
       <c r="G19">
-        <v>70.14</v>
+        <v>75.92</v>
       </c>
       <c r="H19">
-        <v>79.51000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="I19" t="s">
         <v>48</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>69.23</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="G20">
-        <v>69.23</v>
+        <v>75.66</v>
       </c>
       <c r="H20">
-        <v>69.23</v>
+        <v>80.88</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>58.83</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="G21">
-        <v>68.68000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="H21">
-        <v>73.63</v>
+        <v>81.88</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>57.83</v>
+        <v>73.47</v>
       </c>
       <c r="G22">
-        <v>67.25</v>
+        <v>74.72</v>
       </c>
       <c r="H22">
-        <v>74.58</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>54.12</v>
+        <v>66.13</v>
       </c>
       <c r="G23">
-        <v>67.23</v>
+        <v>74.41</v>
       </c>
       <c r="H23">
-        <v>79.38</v>
+        <v>87.78</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>57.08</v>
+        <v>66.31</v>
       </c>
       <c r="G24">
-        <v>67.13</v>
+        <v>74.23</v>
       </c>
       <c r="H24">
-        <v>77.16</v>
+        <v>79.69</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>54.12</v>
+        <v>73.8</v>
       </c>
       <c r="G25">
-        <v>65.97</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="H25">
-        <v>79.38</v>
+        <v>74.12</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>59.35</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="G26">
-        <v>65.36</v>
+        <v>73.84</v>
       </c>
       <c r="H26">
-        <v>71.56</v>
+        <v>77.03</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,19 +1353,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="F27">
-        <v>59.72</v>
+        <v>57.69</v>
       </c>
       <c r="G27">
-        <v>65.13</v>
+        <v>73.52</v>
       </c>
       <c r="H27">
-        <v>70.54000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1382,19 +1382,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="F28">
-        <v>59.81</v>
+        <v>58.16</v>
       </c>
       <c r="G28">
-        <v>65.02</v>
+        <v>73</v>
       </c>
       <c r="H28">
-        <v>69.23</v>
+        <v>86.36</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1414,16 +1414,16 @@
         <v>20</v>
       </c>
       <c r="F29">
-        <v>58.77</v>
+        <v>64.41</v>
       </c>
       <c r="G29">
-        <v>64.45999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="H29">
-        <v>73.48999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1440,19 +1440,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F30">
-        <v>59.92</v>
+        <v>67.75</v>
       </c>
       <c r="G30">
-        <v>63.32</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="H30">
-        <v>68.94</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1469,19 +1469,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>55.17</v>
+        <v>62.7</v>
       </c>
       <c r="G31">
-        <v>63.28</v>
+        <v>70.44</v>
       </c>
       <c r="H31">
-        <v>70.91</v>
+        <v>76.17</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>59.29</v>
+        <v>60.88</v>
       </c>
       <c r="G32">
-        <v>62.99</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="H32">
-        <v>71.20999999999999</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>54.34</v>
+        <v>58.22</v>
       </c>
       <c r="G33">
-        <v>60</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="H33">
-        <v>67.81999999999999</v>
+        <v>70.97</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F34">
-        <v>55.42</v>
+        <v>55.91</v>
       </c>
       <c r="G34">
-        <v>55.42</v>
+        <v>63.54</v>
       </c>
       <c r="H34">
-        <v>55.42</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-21</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
+    <t>1405-06-22</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>12</v>
       </c>
       <c r="F2">
-        <v>86.31</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="G2">
-        <v>101.63</v>
+        <v>100.43</v>
       </c>
       <c r="H2">
-        <v>115.5</v>
+        <v>110.04</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>88.91</v>
+        <v>93.86</v>
       </c>
       <c r="G3">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>103.06</v>
+        <v>103.5</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>70.90000000000001</v>
+        <v>89.62</v>
       </c>
       <c r="G4">
-        <v>97.40000000000001</v>
+        <v>92.44</v>
       </c>
       <c r="H4">
-        <v>116.29</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>86.31</v>
+        <v>81.02</v>
       </c>
       <c r="G5">
-        <v>96.70999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="H5">
-        <v>105.03</v>
+        <v>93.66</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>92.61</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="G6">
-        <v>94.93000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="H6">
-        <v>97.48999999999999</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>88.63</v>
+        <v>80.31</v>
       </c>
       <c r="G7">
-        <v>91.44</v>
+        <v>88.11</v>
       </c>
       <c r="H7">
-        <v>93.36</v>
+        <v>93.8</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>71.97</v>
+        <v>57.88</v>
       </c>
       <c r="G8">
-        <v>84.51000000000001</v>
+        <v>87.33</v>
       </c>
       <c r="H8">
-        <v>97.12</v>
+        <v>106.66</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,13 +834,13 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>63.78</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="G9">
-        <v>84.37</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H9">
-        <v>94.94</v>
+        <v>84.92</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>75.73</v>
+        <v>72.64</v>
       </c>
       <c r="G10">
-        <v>81.06999999999999</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="H10">
-        <v>90.95999999999999</v>
+        <v>88.19</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>76.45999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="G11">
-        <v>80.34999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="H11">
-        <v>82.36</v>
+        <v>85.14</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>80.25</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="G12">
-        <v>80.25</v>
+        <v>77.92</v>
       </c>
       <c r="H12">
-        <v>80.25</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>67.95999999999999</v>
+        <v>72.03</v>
       </c>
       <c r="G13">
-        <v>79.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="H13">
-        <v>90.8</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,13 +979,13 @@
         <v>62</v>
       </c>
       <c r="F14">
-        <v>69.86</v>
+        <v>65.11</v>
       </c>
       <c r="G14">
-        <v>78.38</v>
+        <v>77.03</v>
       </c>
       <c r="H14">
-        <v>89.84999999999999</v>
+        <v>97.58</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>70.27</v>
+        <v>76.64</v>
       </c>
       <c r="G15">
-        <v>77.73</v>
+        <v>76.64</v>
       </c>
       <c r="H15">
-        <v>86.83</v>
+        <v>76.64</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>69.73</v>
+        <v>72.83</v>
       </c>
       <c r="G16">
-        <v>77.73</v>
+        <v>76.31</v>
       </c>
       <c r="H16">
-        <v>83.72</v>
+        <v>82.67</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="F17">
-        <v>71.53</v>
+        <v>62.55</v>
       </c>
       <c r="G17">
-        <v>76.73999999999999</v>
+        <v>76.22</v>
       </c>
       <c r="H17">
-        <v>79.86</v>
+        <v>97.58</v>
       </c>
       <c r="I17" t="s">
         <v>48</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>66.42</v>
+        <v>66.59</v>
       </c>
       <c r="G18">
-        <v>76.34</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H18">
-        <v>86.42</v>
+        <v>86.64</v>
       </c>
       <c r="I18" t="s">
         <v>48</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>75.92</v>
+        <v>57.45</v>
       </c>
       <c r="G19">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="H19">
-        <v>75.92</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="I19" t="s">
         <v>48</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>71.45999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="G20">
-        <v>75.66</v>
+        <v>74.91</v>
       </c>
       <c r="H20">
-        <v>80.88</v>
+        <v>79.97</v>
       </c>
       <c r="I20" t="s">
         <v>48</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>70.70999999999999</v>
+        <v>70.13</v>
       </c>
       <c r="G21">
-        <v>74.76000000000001</v>
+        <v>74.73</v>
       </c>
       <c r="H21">
-        <v>81.88</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s">
         <v>48</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F22">
-        <v>73.47</v>
+        <v>67.95</v>
       </c>
       <c r="G22">
-        <v>74.72</v>
+        <v>73.88</v>
       </c>
       <c r="H22">
-        <v>77.51000000000001</v>
+        <v>83.95</v>
       </c>
       <c r="I22" t="s">
         <v>48</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>66.13</v>
+        <v>70.09</v>
       </c>
       <c r="G23">
-        <v>74.41</v>
+        <v>73.27</v>
       </c>
       <c r="H23">
-        <v>87.78</v>
+        <v>77.05</v>
       </c>
       <c r="I23" t="s">
         <v>48</v>
@@ -1269,13 +1269,13 @@
         <v>20</v>
       </c>
       <c r="F24">
-        <v>66.31</v>
+        <v>63.46</v>
       </c>
       <c r="G24">
-        <v>74.23</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="H24">
-        <v>79.69</v>
+        <v>82.36</v>
       </c>
       <c r="I24" t="s">
         <v>48</v>
@@ -1298,13 +1298,13 @@
         <v>2</v>
       </c>
       <c r="F25">
-        <v>73.8</v>
+        <v>71.45</v>
       </c>
       <c r="G25">
-        <v>73.95999999999999</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="H25">
-        <v>74.12</v>
+        <v>73.62</v>
       </c>
       <c r="I25" t="s">
         <v>48</v>
@@ -1327,13 +1327,13 @@
         <v>13</v>
       </c>
       <c r="F26">
-        <v>64.23999999999999</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="G26">
-        <v>73.84</v>
+        <v>72.53</v>
       </c>
       <c r="H26">
-        <v>77.03</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="I26" t="s">
         <v>48</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>57.69</v>
+        <v>64.08</v>
       </c>
       <c r="G27">
-        <v>73.52</v>
+        <v>72.36</v>
       </c>
       <c r="H27">
-        <v>87.56999999999999</v>
+        <v>75.58</v>
       </c>
       <c r="I27" t="s">
         <v>48</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>58.16</v>
+        <v>65.14</v>
       </c>
       <c r="G28">
-        <v>73</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="H28">
-        <v>86.36</v>
+        <v>82.09</v>
       </c>
       <c r="I28" t="s">
         <v>48</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>64.41</v>
+        <v>64.83</v>
       </c>
       <c r="G29">
-        <v>72.23</v>
+        <v>71.64</v>
       </c>
       <c r="H29">
-        <v>79.76000000000001</v>
+        <v>78.48</v>
       </c>
       <c r="I29" t="s">
         <v>48</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F30">
-        <v>67.75</v>
+        <v>66.58</v>
       </c>
       <c r="G30">
-        <v>71.01000000000001</v>
+        <v>70.91</v>
       </c>
       <c r="H30">
-        <v>75.54000000000001</v>
+        <v>76.23</v>
       </c>
       <c r="I30" t="s">
         <v>48</v>
@@ -1469,19 +1469,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>62.7</v>
+        <v>67.91</v>
       </c>
       <c r="G31">
-        <v>70.44</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="H31">
-        <v>76.17</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>60.88</v>
+        <v>61.23</v>
       </c>
       <c r="G32">
-        <v>68.48999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="H32">
-        <v>78.01000000000001</v>
+        <v>72.62</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F33">
-        <v>58.22</v>
+        <v>55.11</v>
       </c>
       <c r="G33">
-        <v>64.73999999999999</v>
+        <v>62.76</v>
       </c>
       <c r="H33">
-        <v>70.97</v>
+        <v>74.62</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>55.91</v>
+        <v>51.79</v>
       </c>
       <c r="G34">
-        <v>63.54</v>
+        <v>57.6</v>
       </c>
       <c r="H34">
-        <v>76.68000000000001</v>
+        <v>62.94</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
